--- a/packages/calculators/src/modules/test/3.3-dairy-enteric.xlsx
+++ b/packages/calculators/src/modules/test/3.3-dairy-enteric.xlsx
@@ -1,22 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eddiesholl/Code/aginnovationaustralia/emissions-calculators/packages/calculators/src/modules/test/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eddiesholl/Code/aginnovationaustralia/emissions-calculators-internal/packages/calculators/src/modules/test/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FE39238-4D97-BB42-80BD-29DCE045B365}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{655AD9B2-1947-3C40-82A8-C6A8CA4971A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="51220" yWindow="8540" windowWidth="28800" windowHeight="23320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="3.3.1.1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -1124,7 +1123,7 @@
       </c>
       <c r="AG11">
         <f>SUM(AF11:AF17)*10^-3</f>
-        <v>11.576072084045697</v>
+        <v>11.223683133050912</v>
       </c>
       <c r="AM11" t="s">
         <v>24</v>
@@ -1176,8 +1175,12 @@
         <f t="shared" ref="S12:S17" si="3">E12*R12*G12</f>
         <v>1121.0652247167357</v>
       </c>
+      <c r="AC12">
+        <f t="shared" ref="AC12:AC17" si="4">$AN$8</f>
+        <v>0.75</v>
+      </c>
       <c r="AF12">
-        <f t="shared" ref="AF12:AF17" si="4">S12+U12</f>
+        <f t="shared" ref="AF12:AF17" si="5">S12+U12</f>
         <v>1121.0652247167357</v>
       </c>
       <c r="AM12" t="s">
@@ -1225,14 +1228,6 @@
         <f t="shared" si="0"/>
         <v>4.0231734662249998</v>
       </c>
-      <c r="R13">
-        <f t="shared" si="2"/>
-        <v>8.3279690750857505E-2</v>
-      </c>
-      <c r="S13">
-        <f t="shared" si="3"/>
-        <v>69.954940230720297</v>
-      </c>
       <c r="T13">
         <f>$AM$50</f>
         <v>1.7600000000000001E-2</v>
@@ -1241,9 +1236,13 @@
         <f>E13*T13*G13</f>
         <v>14.784000000000001</v>
       </c>
+      <c r="AC13">
+        <f t="shared" si="4"/>
+        <v>0.75</v>
+      </c>
       <c r="AF13">
-        <f t="shared" si="4"/>
-        <v>84.738940230720303</v>
+        <f t="shared" si="5"/>
+        <v>14.784000000000001</v>
       </c>
       <c r="AL13">
         <v>257</v>
@@ -1302,11 +1301,15 @@
         <v>468.03186201981919</v>
       </c>
       <c r="U14">
-        <f t="shared" ref="U14:U16" si="5">E14*T14*G14</f>
-        <v>0</v>
+        <f t="shared" ref="U14:U16" si="6">E14*T14*G14</f>
+        <v>0</v>
+      </c>
+      <c r="AC14">
+        <f t="shared" si="4"/>
+        <v>0.75</v>
       </c>
       <c r="AF14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>468.03186201981919</v>
       </c>
     </row>
@@ -1354,11 +1357,15 @@
         <v>2728.1460599549996</v>
       </c>
       <c r="U15">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AC15">
+        <f t="shared" si="4"/>
+        <v>0.75</v>
+      </c>
+      <c r="AF15">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="AF15">
-        <f t="shared" si="4"/>
         <v>2728.1460599549996</v>
       </c>
     </row>
@@ -1400,25 +1407,21 @@
         <f t="shared" si="0"/>
         <v>5.4143472656250013</v>
       </c>
-      <c r="R16">
-        <f t="shared" si="2"/>
-        <v>0.11207698839843752</v>
-      </c>
-      <c r="S16">
-        <f t="shared" si="3"/>
-        <v>282.43401076406252</v>
-      </c>
       <c r="T16">
         <f>$AM$51</f>
         <v>2.0400000000000001E-2</v>
       </c>
       <c r="U16">
+        <f t="shared" si="6"/>
+        <v>51.408000000000008</v>
+      </c>
+      <c r="AC16">
+        <f t="shared" si="4"/>
+        <v>0.75</v>
+      </c>
+      <c r="AF16">
         <f t="shared" si="5"/>
         <v>51.408000000000008</v>
-      </c>
-      <c r="AF16">
-        <f t="shared" si="4"/>
-        <v>333.84201076406254</v>
       </c>
     </row>
     <row r="17" spans="1:41" x14ac:dyDescent="0.2">
@@ -1467,8 +1470,12 @@
         <f t="shared" si="3"/>
         <v>629.87267479921888</v>
       </c>
+      <c r="AC17">
+        <f t="shared" si="4"/>
+        <v>0.75</v>
+      </c>
       <c r="AF17">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>629.87267479921888</v>
       </c>
       <c r="AL17" t="s">
@@ -1562,7 +1569,7 @@
         <v>7.1849041227053947</v>
       </c>
       <c r="Q21">
-        <f t="shared" ref="Q21:Q27" si="6">(1.185 + 0.00454 *I21- 0.0000026 *I21^2 + 0.315 *K21)^2 *M21 + P21</f>
+        <f t="shared" ref="Q21:Q27" si="7">(1.185 + 0.00454 *I21- 0.0000026 *I21^2 + 0.315 *K21)^2 *M21 + P21</f>
         <v>16.940498588465395</v>
       </c>
       <c r="R21">
@@ -1602,12 +1609,12 @@
         <v>0.6</v>
       </c>
       <c r="AF21">
-        <f>S21+U21</f>
+        <f t="shared" ref="AF21:AF27" si="8">S21+U21</f>
         <v>6399.696854257515</v>
       </c>
       <c r="AG21">
         <f>SUM(AF21:AF27)*10^-3</f>
-        <v>11.867918301699467</v>
+        <v>11.511609866020031</v>
       </c>
       <c r="AL21" s="2" t="s">
         <v>51</v>
@@ -1644,7 +1651,7 @@
         <v>0.6</v>
       </c>
       <c r="M22">
-        <f t="shared" ref="M22:M27" si="7">$AM$46</f>
+        <f t="shared" ref="M22:M27" si="9">$AM$46</f>
         <v>1</v>
       </c>
       <c r="O22">
@@ -1654,19 +1661,23 @@
         <v>0</v>
       </c>
       <c r="Q22">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>7.8978703992249981</v>
       </c>
       <c r="R22">
-        <f t="shared" ref="R22:R27" si="8">20.7 * Q22 * 10^-3</f>
+        <f t="shared" ref="R22:R27" si="10">20.7 * Q22 * 10^-3</f>
         <v>0.16348591726395745</v>
       </c>
       <c r="S22">
-        <f t="shared" ref="S22:S27" si="9">E22*R22*G22</f>
+        <f t="shared" ref="S22:S27" si="11">E22*R22*G22</f>
         <v>1193.4471960268893</v>
       </c>
+      <c r="AC22">
+        <f t="shared" ref="AC22:AC27" si="12">$AN$8</f>
+        <v>0.75</v>
+      </c>
       <c r="AF22">
-        <f>S22+U22</f>
+        <f t="shared" si="8"/>
         <v>1193.4471960268893</v>
       </c>
       <c r="AL22" s="2" t="s">
@@ -1707,26 +1718,18 @@
         <v>0.56999999999999995</v>
       </c>
       <c r="M23">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="O23">
+        <v>0</v>
+      </c>
+      <c r="P23">
+        <v>0</v>
+      </c>
+      <c r="Q23">
         <f t="shared" si="7"/>
-        <v>1</v>
-      </c>
-      <c r="O23">
-        <v>0</v>
-      </c>
-      <c r="P23">
-        <v>0</v>
-      </c>
-      <c r="Q23">
-        <f t="shared" si="6"/>
         <v>4.2485866641000003</v>
-      </c>
-      <c r="R23">
-        <f t="shared" si="8"/>
-        <v>8.7945743946870006E-2</v>
-      </c>
-      <c r="S23">
-        <f t="shared" si="9"/>
-        <v>73.87442491537081</v>
       </c>
       <c r="T23">
         <f>$AM$50</f>
@@ -1736,9 +1739,13 @@
         <f>E23*T23*G23</f>
         <v>14.784000000000001</v>
       </c>
+      <c r="AC23">
+        <f t="shared" si="12"/>
+        <v>0.75</v>
+      </c>
       <c r="AF23">
-        <f>S23+U23</f>
-        <v>88.658424915370816</v>
+        <f t="shared" si="8"/>
+        <v>14.784000000000001</v>
       </c>
       <c r="AL23" s="2" t="s">
         <v>53</v>
@@ -1778,33 +1785,37 @@
         <v>0.56999999999999995</v>
       </c>
       <c r="M24">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="O24">
+        <v>0</v>
+      </c>
+      <c r="P24">
+        <v>0</v>
+      </c>
+      <c r="Q24">
         <f t="shared" si="7"/>
-        <v>1</v>
-      </c>
-      <c r="O24">
-        <v>0</v>
-      </c>
-      <c r="P24">
-        <v>0</v>
-      </c>
-      <c r="Q24">
-        <f t="shared" si="6"/>
         <v>4.2485866641000003</v>
       </c>
       <c r="R24">
+        <f t="shared" si="10"/>
+        <v>8.7945743946870006E-2</v>
+      </c>
+      <c r="S24">
+        <f t="shared" si="11"/>
+        <v>494.25508098140944</v>
+      </c>
+      <c r="U24">
+        <f t="shared" ref="U24:U26" si="13">E24*T24*G24</f>
+        <v>0</v>
+      </c>
+      <c r="AC24">
+        <f t="shared" si="12"/>
+        <v>0.75</v>
+      </c>
+      <c r="AF24">
         <f t="shared" si="8"/>
-        <v>8.7945743946870006E-2</v>
-      </c>
-      <c r="S24">
-        <f t="shared" si="9"/>
-        <v>494.25508098140944</v>
-      </c>
-      <c r="U24">
-        <f t="shared" ref="U24:U26" si="10">E24*T24*G24</f>
-        <v>0</v>
-      </c>
-      <c r="AF24">
-        <f>S24+U24</f>
         <v>494.25508098140944</v>
       </c>
       <c r="AL24" s="2" t="s">
@@ -1842,33 +1853,37 @@
         <v>0.1</v>
       </c>
       <c r="M25">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="O25">
+        <v>0</v>
+      </c>
+      <c r="P25">
+        <v>0</v>
+      </c>
+      <c r="Q25">
         <f t="shared" si="7"/>
-        <v>1</v>
-      </c>
-      <c r="O25">
-        <v>0</v>
-      </c>
-      <c r="P25">
-        <v>0</v>
-      </c>
-      <c r="Q25">
-        <f t="shared" si="6"/>
         <v>9.0270202499999979</v>
       </c>
       <c r="R25">
+        <f t="shared" si="10"/>
+        <v>0.18685931917499995</v>
+      </c>
+      <c r="S25">
+        <f t="shared" si="11"/>
+        <v>2728.1460599549996</v>
+      </c>
+      <c r="U25">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AC25">
+        <f t="shared" si="12"/>
+        <v>0.75</v>
+      </c>
+      <c r="AF25">
         <f t="shared" si="8"/>
-        <v>0.18685931917499995</v>
-      </c>
-      <c r="S25">
-        <f t="shared" si="9"/>
-        <v>2728.1460599549996</v>
-      </c>
-      <c r="U25">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AF25">
-        <f>S25+U25</f>
         <v>2728.1460599549996</v>
       </c>
       <c r="AL25" s="2" t="s">
@@ -1909,38 +1924,34 @@
         <v>0.8</v>
       </c>
       <c r="M26">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="O26">
+        <v>0</v>
+      </c>
+      <c r="P26">
+        <v>0</v>
+      </c>
+      <c r="Q26">
         <f t="shared" si="7"/>
-        <v>1</v>
-      </c>
-      <c r="O26">
-        <v>0</v>
-      </c>
-      <c r="P26">
-        <v>0</v>
-      </c>
-      <c r="Q26">
-        <f t="shared" si="6"/>
         <v>5.4143472656250013</v>
-      </c>
-      <c r="R26">
-        <f t="shared" si="8"/>
-        <v>0.11207698839843752</v>
-      </c>
-      <c r="S26">
-        <f t="shared" si="9"/>
-        <v>282.43401076406252</v>
       </c>
       <c r="T26">
         <f>$AM$51</f>
         <v>2.0400000000000001E-2</v>
       </c>
       <c r="U26">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>51.408000000000008</v>
       </c>
+      <c r="AC26">
+        <f t="shared" si="12"/>
+        <v>0.75</v>
+      </c>
       <c r="AF26">
-        <f>S26+U26</f>
-        <v>333.84201076406254</v>
+        <f t="shared" si="8"/>
+        <v>51.408000000000008</v>
       </c>
       <c r="AL26" s="2" t="s">
         <v>56</v>
@@ -1980,29 +1991,33 @@
         <v>0.8</v>
       </c>
       <c r="M27">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="O27">
+        <v>0</v>
+      </c>
+      <c r="P27">
+        <v>0</v>
+      </c>
+      <c r="Q27">
         <f t="shared" si="7"/>
-        <v>1</v>
-      </c>
-      <c r="O27">
-        <v>0</v>
-      </c>
-      <c r="P27">
-        <v>0</v>
-      </c>
-      <c r="Q27">
-        <f t="shared" si="6"/>
         <v>5.4143472656250013</v>
       </c>
       <c r="R27">
+        <f t="shared" si="10"/>
+        <v>0.11207698839843752</v>
+      </c>
+      <c r="S27">
+        <f t="shared" si="11"/>
+        <v>629.87267479921888</v>
+      </c>
+      <c r="AC27">
+        <f t="shared" si="12"/>
+        <v>0.75</v>
+      </c>
+      <c r="AF27">
         <f t="shared" si="8"/>
-        <v>0.11207698839843752</v>
-      </c>
-      <c r="S27">
-        <f t="shared" si="9"/>
-        <v>629.87267479921888</v>
-      </c>
-      <c r="AF27">
-        <f>S27+U27</f>
         <v>629.87267479921888</v>
       </c>
       <c r="AL27" s="2" t="s">
@@ -2060,7 +2075,7 @@
         <v>7.1849041227053947</v>
       </c>
       <c r="Q31">
-        <f t="shared" ref="Q31:Q37" si="11">(1.185 + 0.00454 *I31- 0.0000026 *I31^2 + 0.315 *K31)^2 *M31 + P31</f>
+        <f t="shared" ref="Q31:Q37" si="14">(1.185 + 0.00454 *I31- 0.0000026 *I31^2 + 0.315 *K31)^2 *M31 + P31</f>
         <v>17.367658739465398</v>
       </c>
       <c r="R31">
@@ -2105,7 +2120,7 @@
       </c>
       <c r="AG31">
         <f>SUM(AF31:AF37)*10^-3</f>
-        <v>12.12866624934926</v>
+        <v>11.768417597198876</v>
       </c>
       <c r="AM31" s="2" t="s">
         <v>41</v>
@@ -2136,7 +2151,7 @@
         <v>0.6</v>
       </c>
       <c r="M32">
-        <f t="shared" ref="M32:M37" si="12">$AM$46</f>
+        <f t="shared" ref="M32:M37" si="15">$AM$46</f>
         <v>1</v>
       </c>
       <c r="O32">
@@ -2146,19 +2161,23 @@
         <v>0</v>
       </c>
       <c r="Q32">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>8.3549902499999984</v>
       </c>
       <c r="R32">
-        <f t="shared" ref="R32:R37" si="13">20.7 * Q32 * 10^-3</f>
+        <f t="shared" ref="R32:R37" si="16">20.7 * Q32 * 10^-3</f>
         <v>0.17294829817499996</v>
       </c>
       <c r="S32">
-        <f t="shared" ref="S32:S37" si="14">E32*R32*G32</f>
+        <f t="shared" ref="S32:S37" si="17">E32*R32*G32</f>
         <v>1262.5225766774997</v>
       </c>
+      <c r="AC32">
+        <f t="shared" ref="AC32:AC37" si="18">$AN$8</f>
+        <v>0.75</v>
+      </c>
       <c r="AF32">
-        <f t="shared" ref="AF32:AF37" si="15">S32+U32</f>
+        <f t="shared" ref="AF32:AF37" si="19">S32+U32</f>
         <v>1262.5225766774997</v>
       </c>
       <c r="AL32" s="2" t="s">
@@ -2196,7 +2215,7 @@
         <v>0.56999999999999995</v>
       </c>
       <c r="M33">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="O33">
@@ -2206,16 +2225,8 @@
         <v>0</v>
       </c>
       <c r="Q33">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>4.4751921662249998</v>
-      </c>
-      <c r="R33">
-        <f t="shared" si="13"/>
-        <v>9.2636477840857503E-2</v>
-      </c>
-      <c r="S33">
-        <f t="shared" si="14"/>
-        <v>77.814641386320304</v>
       </c>
       <c r="T33">
         <f>$AM$50</f>
@@ -2225,9 +2236,13 @@
         <f>E33*T33*G33</f>
         <v>14.784000000000001</v>
       </c>
+      <c r="AC33">
+        <f t="shared" si="18"/>
+        <v>0.75</v>
+      </c>
       <c r="AF33">
-        <f t="shared" si="15"/>
-        <v>92.59864138632031</v>
+        <f t="shared" si="19"/>
+        <v>14.784000000000001</v>
       </c>
     </row>
     <row r="34" spans="1:42" x14ac:dyDescent="0.2">
@@ -2255,7 +2270,7 @@
         <v>0.56999999999999995</v>
       </c>
       <c r="M34">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="O34">
@@ -2265,23 +2280,27 @@
         <v>0</v>
       </c>
       <c r="Q34">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>4.4751921662249998</v>
       </c>
       <c r="R34">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>9.2636477840857503E-2</v>
       </c>
       <c r="S34">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>520.61700546561917</v>
       </c>
       <c r="U34">
-        <f t="shared" ref="U34:U36" si="16">E34*T34*G34</f>
-        <v>0</v>
+        <f t="shared" ref="U34:U36" si="20">E34*T34*G34</f>
+        <v>0</v>
+      </c>
+      <c r="AC34">
+        <f t="shared" si="18"/>
+        <v>0.75</v>
       </c>
       <c r="AF34">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>520.61700546561917</v>
       </c>
       <c r="AP34" s="2"/>
@@ -2308,7 +2327,7 @@
         <v>0.1</v>
       </c>
       <c r="M35">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="O35">
@@ -2318,23 +2337,27 @@
         <v>0</v>
       </c>
       <c r="Q35">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>9.0270202499999979</v>
       </c>
       <c r="R35">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>0.18685931917499995</v>
       </c>
       <c r="S35">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>2728.1460599549996</v>
       </c>
       <c r="U35">
-        <f t="shared" si="16"/>
-        <v>0</v>
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="AC35">
+        <f t="shared" si="18"/>
+        <v>0.75</v>
       </c>
       <c r="AF35">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>2728.1460599549996</v>
       </c>
       <c r="AM35" t="s">
@@ -2369,7 +2392,7 @@
         <v>0.8</v>
       </c>
       <c r="M36">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="O36">
@@ -2379,28 +2402,24 @@
         <v>0</v>
       </c>
       <c r="Q36">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>5.4143472656250013</v>
-      </c>
-      <c r="R36">
-        <f t="shared" si="13"/>
-        <v>0.11207698839843752</v>
-      </c>
-      <c r="S36">
-        <f t="shared" si="14"/>
-        <v>282.43401076406252</v>
       </c>
       <c r="T36">
         <f>$AM$51</f>
         <v>2.0400000000000001E-2</v>
       </c>
       <c r="U36">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>51.408000000000008</v>
       </c>
+      <c r="AC36">
+        <f t="shared" si="18"/>
+        <v>0.75</v>
+      </c>
       <c r="AF36">
-        <f t="shared" si="15"/>
-        <v>333.84201076406254</v>
+        <f t="shared" si="19"/>
+        <v>51.408000000000008</v>
       </c>
       <c r="AL36" s="2" t="s">
         <v>58</v>
@@ -2437,7 +2456,7 @@
         <v>0.8</v>
       </c>
       <c r="M37">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="O37">
@@ -2447,19 +2466,23 @@
         <v>0</v>
       </c>
       <c r="Q37">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>5.4143472656250013</v>
       </c>
       <c r="R37">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>0.11207698839843752</v>
       </c>
       <c r="S37">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>629.87267479921888</v>
       </c>
+      <c r="AC37">
+        <f t="shared" si="18"/>
+        <v>0.75</v>
+      </c>
       <c r="AF37">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>629.87267479921888</v>
       </c>
       <c r="AL37" s="2" t="s">
@@ -2545,7 +2568,7 @@
         <v>13.123112552886568</v>
       </c>
       <c r="Q41">
-        <f t="shared" ref="Q41:Q47" si="17">(1.185 + 0.00454 *I41- 0.0000026 *I41^2 + 0.315 *K41)^2 *M41 + P41</f>
+        <f t="shared" ref="Q41:Q47" si="21">(1.185 + 0.00454 *I41- 0.0000026 *I41^2 + 0.315 *K41)^2 *M41 + P41</f>
         <v>22.377558073646568</v>
       </c>
       <c r="R41">
@@ -2590,7 +2613,7 @@
       </c>
       <c r="AG41">
         <f>SUM(AF41:AF47)*10^-3</f>
-        <v>13.798794078572412</v>
+        <v>13.447705850197277</v>
       </c>
     </row>
     <row r="42" spans="1:42" x14ac:dyDescent="0.2">
@@ -2615,7 +2638,7 @@
         <v>0.6</v>
       </c>
       <c r="M42">
-        <f t="shared" ref="M42:M47" si="18">$AM$46</f>
+        <f t="shared" ref="M42:M47" si="22">$AM$46</f>
         <v>1</v>
       </c>
       <c r="O42">
@@ -2625,19 +2648,23 @@
         <v>0</v>
       </c>
       <c r="Q42">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>7.3488432656250007</v>
       </c>
       <c r="R42">
-        <f t="shared" ref="R42:R47" si="19">20.7 * Q42 * 10^-3</f>
+        <f t="shared" ref="R42:R47" si="23">20.7 * Q42 * 10^-3</f>
         <v>0.15212105559843753</v>
       </c>
       <c r="S42">
-        <f t="shared" ref="S42:S47" si="20">E42*R42*G42</f>
+        <f t="shared" ref="S42:S47" si="24">E42*R42*G42</f>
         <v>1110.4837058685939</v>
       </c>
+      <c r="AC42">
+        <f t="shared" ref="AC42:AC47" si="25">$AN$8</f>
+        <v>0.75</v>
+      </c>
       <c r="AF42">
-        <f t="shared" ref="AF42:AF47" si="21">S42+U42</f>
+        <f t="shared" ref="AF42:AF47" si="26">S42+U42</f>
         <v>1110.4837058685939</v>
       </c>
     </row>
@@ -2666,7 +2693,7 @@
         <v>0.56999999999999995</v>
       </c>
       <c r="M43">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>1</v>
       </c>
       <c r="O43">
@@ -2676,16 +2703,8 @@
         <v>0</v>
       </c>
       <c r="Q43">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>3.9483677025000001</v>
-      </c>
-      <c r="R43">
-        <f t="shared" si="19"/>
-        <v>8.173121144175001E-2</v>
-      </c>
-      <c r="S43">
-        <f t="shared" si="20"/>
-        <v>68.65421761107001</v>
       </c>
       <c r="T43">
         <f>$AM$50</f>
@@ -2695,9 +2714,13 @@
         <f>E43*T43*G43</f>
         <v>14.784000000000001</v>
       </c>
+      <c r="AC43">
+        <f t="shared" si="25"/>
+        <v>0.75</v>
+      </c>
       <c r="AF43">
-        <f t="shared" si="21"/>
-        <v>83.438217611070016</v>
+        <f t="shared" si="26"/>
+        <v>14.784000000000001</v>
       </c>
       <c r="AL43" s="2" t="s">
         <v>64</v>
@@ -2728,7 +2751,7 @@
         <v>0.56999999999999995</v>
       </c>
       <c r="M44">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>1</v>
       </c>
       <c r="O44">
@@ -2738,23 +2761,27 @@
         <v>0</v>
       </c>
       <c r="Q44">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>3.9483677025000001</v>
       </c>
       <c r="R44">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v>8.173121144175001E-2</v>
       </c>
       <c r="S44">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v>459.32940830263504</v>
       </c>
       <c r="U44">
-        <f t="shared" ref="U44:U46" si="22">E44*T44*G44</f>
-        <v>0</v>
+        <f t="shared" ref="U44:U46" si="27">E44*T44*G44</f>
+        <v>0</v>
+      </c>
+      <c r="AC44">
+        <f t="shared" si="25"/>
+        <v>0.75</v>
       </c>
       <c r="AF44">
-        <f t="shared" si="21"/>
+        <f t="shared" si="26"/>
         <v>459.32940830263504</v>
       </c>
       <c r="AL44" s="2" t="s">
@@ -2783,7 +2810,7 @@
         <v>0.1</v>
       </c>
       <c r="M45">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>1</v>
       </c>
       <c r="O45">
@@ -2793,23 +2820,27 @@
         <v>0</v>
       </c>
       <c r="Q45">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>9.0270202499999979</v>
       </c>
       <c r="R45">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v>0.18685931917499995</v>
       </c>
       <c r="S45">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v>2728.1460599549996</v>
       </c>
       <c r="U45">
-        <f t="shared" si="22"/>
-        <v>0</v>
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="AC45">
+        <f t="shared" si="25"/>
+        <v>0.75</v>
       </c>
       <c r="AF45">
-        <f t="shared" si="21"/>
+        <f t="shared" si="26"/>
         <v>2728.1460599549996</v>
       </c>
       <c r="AL45" s="2" t="s">
@@ -2844,7 +2875,7 @@
         <v>0.8</v>
       </c>
       <c r="M46">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>1</v>
       </c>
       <c r="O46">
@@ -2854,28 +2885,24 @@
         <v>0</v>
       </c>
       <c r="Q46">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>5.4143472656250013</v>
-      </c>
-      <c r="R46">
-        <f t="shared" si="19"/>
-        <v>0.11207698839843752</v>
-      </c>
-      <c r="S46">
-        <f t="shared" si="20"/>
-        <v>282.43401076406252</v>
       </c>
       <c r="T46">
         <f>$AM$51</f>
         <v>2.0400000000000001E-2</v>
       </c>
       <c r="U46">
-        <f t="shared" si="22"/>
+        <f t="shared" si="27"/>
         <v>51.408000000000008</v>
       </c>
+      <c r="AC46">
+        <f t="shared" si="25"/>
+        <v>0.75</v>
+      </c>
       <c r="AF46">
-        <f t="shared" si="21"/>
-        <v>333.84201076406254</v>
+        <f t="shared" si="26"/>
+        <v>51.408000000000008</v>
       </c>
       <c r="AL46" s="2" t="s">
         <v>65</v>
@@ -2909,7 +2936,7 @@
         <v>0.8</v>
       </c>
       <c r="M47">
-        <f t="shared" si="18"/>
+        <f t="shared" si="22"/>
         <v>1</v>
       </c>
       <c r="O47">
@@ -2919,19 +2946,23 @@
         <v>0</v>
       </c>
       <c r="Q47">
-        <f t="shared" si="17"/>
+        <f t="shared" si="21"/>
         <v>5.4143472656250013</v>
       </c>
       <c r="R47">
-        <f t="shared" si="19"/>
+        <f t="shared" si="23"/>
         <v>0.11207698839843752</v>
       </c>
       <c r="S47">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v>629.87267479921888</v>
       </c>
+      <c r="AC47">
+        <f t="shared" si="25"/>
+        <v>0.75</v>
+      </c>
       <c r="AF47">
-        <f t="shared" si="21"/>
+        <f t="shared" si="26"/>
         <v>629.87267479921888</v>
       </c>
     </row>
@@ -2964,6 +2995,88 @@
       </c>
     </row>
     <row r="51" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A51" t="s">
+        <v>88</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D51" t="s">
+        <v>33</v>
+      </c>
+      <c r="E51">
+        <v>50</v>
+      </c>
+      <c r="G51">
+        <v>365</v>
+      </c>
+      <c r="I51">
+        <f>VLOOKUP(C51,$AL$18:$AO$27, 2, FALSE)</f>
+        <v>480</v>
+      </c>
+      <c r="K51">
+        <f>$AM$36</f>
+        <v>1.6E-2</v>
+      </c>
+      <c r="M51">
+        <f>$AM$45</f>
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="O51">
+        <v>10</v>
+      </c>
+      <c r="P51">
+        <f>(O51 * 1.03 *AA51) / (Z51 * AE51 * AD51)</f>
+        <v>4.7899360818035959</v>
+      </c>
+      <c r="Q51">
+        <f t="shared" ref="Q51:Q57" si="28">(1.185 + 0.00454 *I51- 0.0000026 *I51^2 + 0.315 *K51)^2 *M51 + P51</f>
+        <v>13.231344925803597</v>
+      </c>
+      <c r="R51">
+        <f>20.7 * Q51 * 10^-3</f>
+        <v>0.27388883996413443</v>
+      </c>
+      <c r="S51">
+        <f>E51*R51*G51</f>
+        <v>4998.4713293454533</v>
+      </c>
+      <c r="W51">
+        <f>$AN$12</f>
+        <v>4</v>
+      </c>
+      <c r="Y51">
+        <f>$AN$11</f>
+        <v>3.3</v>
+      </c>
+      <c r="Z51">
+        <f>$AN$10</f>
+        <v>18.399999999999999</v>
+      </c>
+      <c r="AA51">
+        <f>$AN$13</f>
+        <v>3.0539999999999998</v>
+      </c>
+      <c r="AC51">
+        <f>$AN$8</f>
+        <v>0.75</v>
+      </c>
+      <c r="AD51">
+        <f>0.795 * AC51- 0.0014</f>
+        <v>0.5948500000000001</v>
+      </c>
+      <c r="AE51">
+        <f>$AN$9</f>
+        <v>0.6</v>
+      </c>
+      <c r="AF51">
+        <f>S51+U51</f>
+        <v>4998.4713293454533</v>
+      </c>
+      <c r="AG51">
+        <f>SUM(AF51:AF57)*10^-3</f>
+        <v>9.8886274223547375</v>
+      </c>
       <c r="AL51" s="2" t="s">
         <v>75</v>
       </c>
@@ -2977,433 +3090,336 @@
         <v>9.1999999999999998E-3</v>
       </c>
     </row>
-    <row r="61" spans="1:41" x14ac:dyDescent="0.2">
-      <c r="A61" t="s">
-        <v>83</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="D61" t="s">
-        <v>33</v>
-      </c>
-      <c r="E61">
-        <v>50</v>
-      </c>
-      <c r="F61">
-        <v>350</v>
-      </c>
-      <c r="G61" s="3">
-        <v>350</v>
-      </c>
-      <c r="I61">
-        <f>VLOOKUP(C61,$AL$18:$AO$27, 2, FALSE)</f>
-        <v>650</v>
-      </c>
-      <c r="K61">
-        <f>$AM$36</f>
-        <v>1.6E-2</v>
-      </c>
-      <c r="M61">
-        <f>$AM$45</f>
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="O61">
-        <v>15</v>
-      </c>
-      <c r="P61">
-        <f>(O61 * 1.03 *AA61) / (Z61 * AE61 * AD61)</f>
-        <v>7.1849041227053947</v>
-      </c>
-      <c r="Q61">
-        <f t="shared" ref="Q61:Q67" si="23">(1.185 + 0.00454 *I61- 0.0000026 *I61^2 + 0.315 *K61)^2 *M61 + P61</f>
-        <v>17.367658739465398</v>
-      </c>
-      <c r="R61">
-        <f>20.7 * Q61 * 10^-3</f>
-        <v>0.35951053590693377</v>
-      </c>
-      <c r="S61">
-        <f>E61*R61*G61</f>
-        <v>6291.4343783713412</v>
-      </c>
-      <c r="W61">
-        <f>$AN$12</f>
-        <v>4</v>
-      </c>
-      <c r="Y61">
-        <f>$AN$11</f>
-        <v>3.3</v>
-      </c>
-      <c r="Z61">
-        <f>$AN$10</f>
-        <v>18.399999999999999</v>
-      </c>
-      <c r="AA61">
-        <f>$AN$13</f>
-        <v>3.0539999999999998</v>
-      </c>
-      <c r="AC61">
-        <f>$AN$8</f>
-        <v>0.75</v>
-      </c>
-      <c r="AD61">
-        <f>0.795 * AC61- 0.0014</f>
-        <v>0.5948500000000001</v>
-      </c>
-      <c r="AE61">
-        <f>$AN$9</f>
-        <v>0.6</v>
-      </c>
-      <c r="AF61">
-        <f>S61+U61</f>
-        <v>6291.4343783713412</v>
-      </c>
-      <c r="AG61">
-        <f>SUM(AF61:AF67)*10^-3</f>
-        <v>11.593500680151759</v>
-      </c>
-    </row>
-    <row r="62" spans="1:41" x14ac:dyDescent="0.2">
-      <c r="A62">
+    <row r="52" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A52">
         <v>2</v>
       </c>
-      <c r="D62" t="s">
+      <c r="D52" t="s">
         <v>34</v>
       </c>
-      <c r="E62">
+      <c r="E52">
         <v>20</v>
       </c>
-      <c r="F62">
+      <c r="G52">
         <v>365</v>
       </c>
-      <c r="G62" s="3">
-        <v>365</v>
-      </c>
-      <c r="I62">
-        <f>VLOOKUP(C61,$AL$18:$AO$27, 3, FALSE)</f>
-        <v>450</v>
-      </c>
-      <c r="K62">
+      <c r="I52">
+        <f>VLOOKUP(C51,$AL$18:$AO$27, 3, FALSE)</f>
+        <v>335</v>
+      </c>
+      <c r="K52">
         <f>$AM$37</f>
         <v>0.6</v>
       </c>
-      <c r="M62">
-        <f t="shared" ref="M62:M67" si="24">$AM$46</f>
-        <v>1</v>
-      </c>
-      <c r="O62">
-        <v>0</v>
-      </c>
-      <c r="P62">
-        <v>0</v>
-      </c>
-      <c r="Q62">
-        <f t="shared" si="23"/>
-        <v>8.3549902499999984</v>
-      </c>
-      <c r="R62">
-        <f t="shared" ref="R62:R67" si="25">20.7 * Q62 * 10^-3</f>
-        <v>0.17294829817499996</v>
-      </c>
-      <c r="S62">
-        <f t="shared" ref="S62:S67" si="26">E62*R62*G62</f>
-        <v>1262.5225766774997</v>
-      </c>
-      <c r="AF62">
-        <f t="shared" ref="AF62:AF67" si="27">S62+U62</f>
-        <v>1262.5225766774997</v>
-      </c>
-    </row>
-    <row r="63" spans="1:41" x14ac:dyDescent="0.2">
-      <c r="A63">
+      <c r="M52">
+        <f t="shared" ref="M52:M57" si="29">$AM$46</f>
+        <v>1</v>
+      </c>
+      <c r="O52">
+        <v>0</v>
+      </c>
+      <c r="P52">
+        <v>0</v>
+      </c>
+      <c r="Q52">
+        <f t="shared" si="28"/>
+        <v>6.7762077032249994</v>
+      </c>
+      <c r="R52">
+        <f t="shared" ref="R52:R57" si="30">20.7 * Q52 * 10^-3</f>
+        <v>0.14026749945675748</v>
+      </c>
+      <c r="S52">
+        <f t="shared" ref="S52:S57" si="31">E52*R52*G52</f>
+        <v>1023.9527460343295</v>
+      </c>
+      <c r="AC52">
+        <f t="shared" ref="AC52:AC57" si="32">$AN$8</f>
+        <v>0.75</v>
+      </c>
+      <c r="AF52">
+        <f t="shared" ref="AF52:AF57" si="33">S52+U52</f>
+        <v>1023.9527460343295</v>
+      </c>
+    </row>
+    <row r="53" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A53">
         <v>3</v>
       </c>
-      <c r="B63" t="s">
+      <c r="B53" t="s">
         <v>70</v>
       </c>
-      <c r="D63" t="s">
+      <c r="D53" t="s">
         <v>35</v>
       </c>
-      <c r="E63">
+      <c r="E53">
         <v>10</v>
       </c>
-      <c r="F63">
-        <v>80</v>
-      </c>
-      <c r="G63" s="3">
-        <v>80</v>
-      </c>
-      <c r="I63">
-        <f>VLOOKUP(C61,$AL$18:$AO$27, 4, FALSE)</f>
-        <v>185</v>
-      </c>
-      <c r="K63">
+      <c r="G53">
+        <v>84</v>
+      </c>
+      <c r="I53">
+        <f>VLOOKUP(C51,$AL$18:$AO$27, 4, FALSE)</f>
+        <v>140</v>
+      </c>
+      <c r="K53">
         <f>$AM$38</f>
         <v>0.56999999999999995</v>
       </c>
-      <c r="M63">
-        <f t="shared" si="24"/>
-        <v>1</v>
-      </c>
-      <c r="O63">
-        <v>0</v>
-      </c>
-      <c r="P63">
-        <v>0</v>
-      </c>
-      <c r="Q63">
-        <f t="shared" si="23"/>
-        <v>4.4751921662249998</v>
-      </c>
-      <c r="R63">
-        <f t="shared" si="25"/>
-        <v>9.2636477840857503E-2</v>
-      </c>
-      <c r="S63">
-        <f t="shared" si="26"/>
-        <v>74.109182272685999</v>
-      </c>
-      <c r="T63">
+      <c r="M53">
+        <f t="shared" si="29"/>
+        <v>1</v>
+      </c>
+      <c r="O53">
+        <v>0</v>
+      </c>
+      <c r="P53">
+        <v>0</v>
+      </c>
+      <c r="Q53">
+        <f t="shared" si="28"/>
+        <v>3.7993416560999989</v>
+      </c>
+      <c r="T53">
         <f>$AM$50</f>
         <v>1.7600000000000001E-2</v>
       </c>
-      <c r="U63">
-        <f>E63*T63*G63</f>
-        <v>14.080000000000002</v>
-      </c>
-      <c r="AF63">
-        <f t="shared" si="27"/>
-        <v>88.189182272685997</v>
-      </c>
-    </row>
-    <row r="64" spans="1:41" x14ac:dyDescent="0.2">
-      <c r="A64">
+      <c r="U53">
+        <f>E53*T53*G53</f>
+        <v>14.784000000000001</v>
+      </c>
+      <c r="AC53">
+        <f t="shared" si="32"/>
+        <v>0.75</v>
+      </c>
+      <c r="AF53">
+        <f t="shared" si="33"/>
+        <v>14.784000000000001</v>
+      </c>
+    </row>
+    <row r="54" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A54">
         <v>3</v>
       </c>
-      <c r="B64" t="s">
+      <c r="B54" t="s">
         <v>71</v>
       </c>
-      <c r="D64" t="s">
+      <c r="D54" t="s">
         <v>35</v>
       </c>
-      <c r="E64">
+      <c r="E54">
         <v>20</v>
       </c>
-      <c r="F64">
-        <v>285</v>
-      </c>
-      <c r="G64" s="3">
-        <v>285</v>
-      </c>
-      <c r="I64">
-        <f>VLOOKUP(C61,$AL$18:$AO$27, 4, FALSE)</f>
-        <v>185</v>
-      </c>
-      <c r="K64">
+      <c r="G54">
+        <v>281</v>
+      </c>
+      <c r="I54">
+        <f>VLOOKUP(C51,$AL$18:$AO$27, 4, FALSE)</f>
+        <v>140</v>
+      </c>
+      <c r="K54">
         <f>$AM$38</f>
         <v>0.56999999999999995</v>
       </c>
-      <c r="M64">
-        <f t="shared" si="24"/>
-        <v>1</v>
-      </c>
-      <c r="O64">
-        <v>0</v>
-      </c>
-      <c r="P64">
-        <v>0</v>
-      </c>
-      <c r="Q64">
-        <f t="shared" si="23"/>
-        <v>4.4751921662249998</v>
-      </c>
-      <c r="R64">
-        <f t="shared" si="25"/>
-        <v>9.2636477840857503E-2</v>
-      </c>
-      <c r="S64">
-        <f t="shared" si="26"/>
-        <v>528.02792369288773</v>
-      </c>
-      <c r="U64">
-        <f t="shared" ref="U64:U66" si="28">E64*T64*G64</f>
-        <v>0</v>
-      </c>
-      <c r="AF64">
-        <f t="shared" si="27"/>
-        <v>528.02792369288773</v>
-      </c>
-    </row>
-    <row r="65" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A65">
+      <c r="M54">
+        <f t="shared" si="29"/>
+        <v>1</v>
+      </c>
+      <c r="O54">
+        <v>0</v>
+      </c>
+      <c r="P54">
+        <v>0</v>
+      </c>
+      <c r="Q54">
+        <f t="shared" si="28"/>
+        <v>3.7993416560999989</v>
+      </c>
+      <c r="R54">
+        <f t="shared" si="30"/>
+        <v>7.8646372281269972E-2</v>
+      </c>
+      <c r="S54">
+        <f t="shared" si="31"/>
+        <v>441.99261222073721</v>
+      </c>
+      <c r="U54">
+        <f t="shared" ref="U54:U56" si="34">E54*T54*G54</f>
+        <v>0</v>
+      </c>
+      <c r="AC54">
+        <f t="shared" si="32"/>
+        <v>0.75</v>
+      </c>
+      <c r="AF54">
+        <f t="shared" si="33"/>
+        <v>441.99261222073721</v>
+      </c>
+    </row>
+    <row r="55" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A55">
         <v>4</v>
       </c>
-      <c r="D65" t="s">
+      <c r="D55" t="s">
         <v>36</v>
       </c>
-      <c r="E65">
+      <c r="E55">
         <v>40</v>
       </c>
-      <c r="F65">
-        <v>330</v>
-      </c>
-      <c r="G65" s="3">
-        <v>330</v>
-      </c>
-      <c r="I65">
+      <c r="G55">
+        <v>365</v>
+      </c>
+      <c r="I55">
         <f>$AM$32</f>
         <v>600</v>
       </c>
-      <c r="K65">
+      <c r="K55">
         <f>$AM$39</f>
         <v>0.1</v>
       </c>
-      <c r="M65">
-        <f t="shared" si="24"/>
-        <v>1</v>
-      </c>
-      <c r="O65">
-        <v>0</v>
-      </c>
-      <c r="P65">
-        <v>0</v>
-      </c>
-      <c r="Q65">
-        <f t="shared" si="23"/>
+      <c r="M55">
+        <f t="shared" si="29"/>
+        <v>1</v>
+      </c>
+      <c r="O55">
+        <v>0</v>
+      </c>
+      <c r="P55">
+        <v>0</v>
+      </c>
+      <c r="Q55">
+        <f t="shared" si="28"/>
         <v>9.0270202499999979</v>
       </c>
-      <c r="R65">
-        <f t="shared" si="25"/>
+      <c r="R55">
+        <f t="shared" si="30"/>
         <v>0.18685931917499995</v>
       </c>
-      <c r="S65">
-        <f t="shared" si="26"/>
-        <v>2466.5430131099993</v>
-      </c>
-      <c r="U65">
-        <f t="shared" si="28"/>
-        <v>0</v>
-      </c>
-      <c r="AF65">
-        <f t="shared" si="27"/>
-        <v>2466.5430131099993</v>
-      </c>
-    </row>
-    <row r="66" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A66">
+      <c r="S55">
+        <f t="shared" si="31"/>
+        <v>2728.1460599549996</v>
+      </c>
+      <c r="U55">
+        <f t="shared" si="34"/>
+        <v>0</v>
+      </c>
+      <c r="AC55">
+        <f t="shared" si="32"/>
+        <v>0.75</v>
+      </c>
+      <c r="AF55">
+        <f t="shared" si="33"/>
+        <v>2728.1460599549996</v>
+      </c>
+    </row>
+    <row r="56" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A56">
         <v>5</v>
       </c>
-      <c r="B66" t="s">
+      <c r="B56" t="s">
         <v>70</v>
       </c>
-      <c r="D66" t="s">
+      <c r="D56" t="s">
         <v>37</v>
       </c>
-      <c r="E66">
+      <c r="E56">
         <v>30</v>
       </c>
-      <c r="F66">
-        <v>80</v>
-      </c>
-      <c r="G66" s="3">
-        <v>80</v>
-      </c>
-      <c r="I66">
+      <c r="G56">
+        <v>84</v>
+      </c>
+      <c r="I56">
         <f>$AN$32</f>
         <v>225</v>
       </c>
-      <c r="K66">
+      <c r="K56">
         <f>$AM$40</f>
         <v>0.8</v>
       </c>
-      <c r="M66">
-        <f t="shared" si="24"/>
-        <v>1</v>
-      </c>
-      <c r="O66">
-        <v>0</v>
-      </c>
-      <c r="P66">
-        <v>0</v>
-      </c>
-      <c r="Q66">
-        <f t="shared" si="23"/>
+      <c r="M56">
+        <f t="shared" si="29"/>
+        <v>1</v>
+      </c>
+      <c r="O56">
+        <v>0</v>
+      </c>
+      <c r="P56">
+        <v>0</v>
+      </c>
+      <c r="Q56">
+        <f t="shared" si="28"/>
         <v>5.4143472656250013</v>
       </c>
-      <c r="R66">
-        <f t="shared" si="25"/>
-        <v>0.11207698839843752</v>
-      </c>
-      <c r="S66">
-        <f t="shared" si="26"/>
-        <v>268.98477215625002</v>
-      </c>
-      <c r="T66">
+      <c r="T56">
         <f>$AM$51</f>
         <v>2.0400000000000001E-2</v>
       </c>
-      <c r="U66">
-        <f t="shared" si="28"/>
-        <v>48.960000000000008</v>
-      </c>
-      <c r="AF66">
-        <f t="shared" si="27"/>
-        <v>317.94477215625</v>
-      </c>
-    </row>
-    <row r="67" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="A67">
+      <c r="U56">
+        <f t="shared" si="34"/>
+        <v>51.408000000000008</v>
+      </c>
+      <c r="AC56">
+        <f t="shared" si="32"/>
+        <v>0.75</v>
+      </c>
+      <c r="AF56">
+        <f t="shared" si="33"/>
+        <v>51.408000000000008</v>
+      </c>
+    </row>
+    <row r="57" spans="1:41" x14ac:dyDescent="0.2">
+      <c r="A57">
         <v>5</v>
       </c>
-      <c r="B67" t="s">
+      <c r="B57" t="s">
         <v>71</v>
       </c>
-      <c r="D67" t="s">
+      <c r="D57" t="s">
         <v>37</v>
       </c>
-      <c r="E67">
+      <c r="E57">
         <v>20</v>
       </c>
-      <c r="F67">
-        <v>285</v>
-      </c>
-      <c r="G67" s="3">
-        <v>285</v>
-      </c>
-      <c r="I67">
+      <c r="G57">
+        <v>281</v>
+      </c>
+      <c r="I57">
         <f>$AN$32</f>
         <v>225</v>
       </c>
-      <c r="K67">
+      <c r="K57">
         <f>$AM$40</f>
         <v>0.8</v>
       </c>
-      <c r="M67">
-        <f t="shared" si="24"/>
-        <v>1</v>
-      </c>
-      <c r="O67">
-        <v>0</v>
-      </c>
-      <c r="P67">
-        <v>0</v>
-      </c>
-      <c r="Q67">
-        <f t="shared" si="23"/>
+      <c r="M57">
+        <f t="shared" si="29"/>
+        <v>1</v>
+      </c>
+      <c r="O57">
+        <v>0</v>
+      </c>
+      <c r="P57">
+        <v>0</v>
+      </c>
+      <c r="Q57">
+        <f t="shared" si="28"/>
         <v>5.4143472656250013</v>
       </c>
-      <c r="R67">
-        <f t="shared" si="25"/>
+      <c r="R57">
+        <f t="shared" si="30"/>
         <v>0.11207698839843752</v>
       </c>
-      <c r="S67">
-        <f t="shared" si="26"/>
-        <v>638.83883387109381</v>
-      </c>
-      <c r="AF67">
-        <f t="shared" si="27"/>
-        <v>638.83883387109381</v>
+      <c r="S57">
+        <f t="shared" si="31"/>
+        <v>629.87267479921888</v>
+      </c>
+      <c r="AC57">
+        <f t="shared" si="32"/>
+        <v>0.75</v>
+      </c>
+      <c r="AF57">
+        <f t="shared" si="33"/>
+        <v>629.87267479921888</v>
       </c>
     </row>
     <row r="71" spans="1:33" x14ac:dyDescent="0.2">
@@ -3419,14 +3435,15 @@
       <c r="E71">
         <v>50</v>
       </c>
-      <c r="G71">
-        <v>365</v>
-      </c>
-      <c r="H71">
-        <v>620</v>
-      </c>
-      <c r="I71" s="3">
-        <v>620</v>
+      <c r="F71">
+        <v>350</v>
+      </c>
+      <c r="G71" s="3">
+        <v>350</v>
+      </c>
+      <c r="I71">
+        <f>VLOOKUP(C71,$AL$18:$AO$27, 2, FALSE)</f>
+        <v>650</v>
       </c>
       <c r="K71">
         <f>$AM$36</f>
@@ -3444,16 +3461,16 @@
         <v>7.1849041227053947</v>
       </c>
       <c r="Q71">
-        <f t="shared" ref="Q71:Q77" si="29">(1.185 + 0.00454 *I71- 0.0000026 *I71^2 + 0.315 *K71)^2 *M71 + P71</f>
-        <v>17.120576198705397</v>
+        <f t="shared" ref="Q71:Q77" si="35">(1.185 + 0.00454 *I71- 0.0000026 *I71^2 + 0.315 *K71)^2 *M71 + P71</f>
+        <v>17.367658739465398</v>
       </c>
       <c r="R71">
         <f>20.7 * Q71 * 10^-3</f>
-        <v>0.35439592731320169</v>
+        <v>0.35951053590693377</v>
       </c>
       <c r="S71">
         <f>E71*R71*G71</f>
-        <v>6467.7256734659304</v>
+        <v>6291.4343783713412</v>
       </c>
       <c r="W71">
         <f>$AN$12</f>
@@ -3485,11 +3502,11 @@
       </c>
       <c r="AF71">
         <f>S71+U71</f>
-        <v>6467.7256734659304</v>
+        <v>6291.4343783713412</v>
       </c>
       <c r="AG71">
         <f>SUM(AF71:AF77)*10^-3</f>
-        <v>11.860526658469761</v>
+        <v>11.25040672572282</v>
       </c>
     </row>
     <row r="72" spans="1:33" x14ac:dyDescent="0.2">
@@ -3502,21 +3519,22 @@
       <c r="E72">
         <v>20</v>
       </c>
-      <c r="G72">
+      <c r="F72">
         <v>365</v>
       </c>
-      <c r="H72">
-        <v>440</v>
-      </c>
-      <c r="I72" s="3">
-        <v>440</v>
+      <c r="G72" s="3">
+        <v>365</v>
+      </c>
+      <c r="I72">
+        <f>VLOOKUP(C71,$AL$18:$AO$27, 3, FALSE)</f>
+        <v>450</v>
       </c>
       <c r="K72">
         <f>$AM$37</f>
         <v>0.6</v>
       </c>
       <c r="M72">
-        <f t="shared" ref="M72:M77" si="30">$AM$46</f>
+        <f t="shared" ref="M72:M77" si="36">$AM$46</f>
         <v>1</v>
       </c>
       <c r="O72">
@@ -3526,20 +3544,24 @@
         <v>0</v>
       </c>
       <c r="Q72">
-        <f t="shared" si="29"/>
-        <v>8.2268006975999999</v>
+        <f t="shared" si="35"/>
+        <v>8.3549902499999984</v>
       </c>
       <c r="R72">
-        <f t="shared" ref="R72:R77" si="31">20.7 * Q72 * 10^-3</f>
-        <v>0.17029477444032001</v>
+        <f t="shared" ref="R72:R77" si="37">20.7 * Q72 * 10^-3</f>
+        <v>0.17294829817499996</v>
       </c>
       <c r="S72">
-        <f t="shared" ref="S72:S77" si="32">E72*R72*G72</f>
-        <v>1243.1518534143361</v>
+        <f t="shared" ref="S72:S77" si="38">E72*R72*G72</f>
+        <v>1262.5225766774997</v>
+      </c>
+      <c r="AC72">
+        <f t="shared" ref="AC72:AC77" si="39">$AN$8</f>
+        <v>0.75</v>
       </c>
       <c r="AF72">
-        <f t="shared" ref="AF72:AF77" si="33">S72+U72</f>
-        <v>1243.1518534143361</v>
+        <f t="shared" ref="AF72:AF77" si="40">S72+U72</f>
+        <v>1262.5225766774997</v>
       </c>
     </row>
     <row r="73" spans="1:33" x14ac:dyDescent="0.2">
@@ -3555,21 +3577,22 @@
       <c r="E73">
         <v>10</v>
       </c>
-      <c r="G73">
-        <v>84</v>
-      </c>
-      <c r="H73">
-        <v>170</v>
-      </c>
-      <c r="I73" s="3">
-        <v>170</v>
+      <c r="F73">
+        <v>80</v>
+      </c>
+      <c r="G73" s="3">
+        <v>80</v>
+      </c>
+      <c r="I73">
+        <f>VLOOKUP(C71,$AL$18:$AO$27, 4, FALSE)</f>
+        <v>185</v>
       </c>
       <c r="K73">
         <f>$AM$38</f>
         <v>0.56999999999999995</v>
       </c>
       <c r="M73">
-        <f t="shared" si="30"/>
+        <f t="shared" si="36"/>
         <v>1</v>
       </c>
       <c r="O73">
@@ -3579,16 +3602,8 @@
         <v>0</v>
       </c>
       <c r="Q73">
-        <f t="shared" si="29"/>
-        <v>4.2485866641000003</v>
-      </c>
-      <c r="R73">
-        <f t="shared" si="31"/>
-        <v>8.7945743946870006E-2</v>
-      </c>
-      <c r="S73">
-        <f t="shared" si="32"/>
-        <v>73.87442491537081</v>
+        <f t="shared" si="35"/>
+        <v>4.4751921662249998</v>
       </c>
       <c r="T73">
         <f>$AM$50</f>
@@ -3596,11 +3611,15 @@
       </c>
       <c r="U73">
         <f>E73*T73*G73</f>
-        <v>14.784000000000001</v>
+        <v>14.080000000000002</v>
+      </c>
+      <c r="AC73">
+        <f t="shared" si="39"/>
+        <v>0.75</v>
       </c>
       <c r="AF73">
-        <f t="shared" si="33"/>
-        <v>88.658424915370816</v>
+        <f t="shared" si="40"/>
+        <v>14.080000000000002</v>
       </c>
     </row>
     <row r="74" spans="1:33" x14ac:dyDescent="0.2">
@@ -3616,21 +3635,22 @@
       <c r="E74">
         <v>20</v>
       </c>
-      <c r="G74">
-        <v>281</v>
-      </c>
-      <c r="H74">
-        <v>175</v>
-      </c>
-      <c r="I74" s="3">
-        <v>175</v>
+      <c r="F74">
+        <v>285</v>
+      </c>
+      <c r="G74" s="3">
+        <v>285</v>
+      </c>
+      <c r="I74">
+        <f>VLOOKUP(C71,$AL$18:$AO$27, 4, FALSE)</f>
+        <v>185</v>
       </c>
       <c r="K74">
         <f>$AM$38</f>
         <v>0.56999999999999995</v>
       </c>
       <c r="M74">
-        <f t="shared" si="30"/>
+        <f t="shared" si="36"/>
         <v>1</v>
       </c>
       <c r="O74">
@@ -3640,24 +3660,28 @@
         <v>0</v>
       </c>
       <c r="Q74">
-        <f t="shared" si="29"/>
-        <v>4.3240083306250003</v>
+        <f t="shared" si="35"/>
+        <v>4.4751921662249998</v>
       </c>
       <c r="R74">
-        <f t="shared" si="31"/>
-        <v>8.9506972443937502E-2</v>
+        <f t="shared" si="37"/>
+        <v>9.2636477840857503E-2</v>
       </c>
       <c r="S74">
-        <f t="shared" si="32"/>
-        <v>503.02918513492875</v>
+        <f t="shared" si="38"/>
+        <v>528.02792369288773</v>
       </c>
       <c r="U74">
-        <f t="shared" ref="U74:U76" si="34">E74*T74*G74</f>
-        <v>0</v>
+        <f t="shared" ref="U74:U76" si="41">E74*T74*G74</f>
+        <v>0</v>
+      </c>
+      <c r="AC74">
+        <f t="shared" si="39"/>
+        <v>0.75</v>
       </c>
       <c r="AF74">
-        <f t="shared" si="33"/>
-        <v>503.02918513492875</v>
+        <f t="shared" si="40"/>
+        <v>528.02792369288773</v>
       </c>
     </row>
     <row r="75" spans="1:33" x14ac:dyDescent="0.2">
@@ -3670,21 +3694,22 @@
       <c r="E75">
         <v>40</v>
       </c>
-      <c r="G75">
-        <v>365</v>
-      </c>
-      <c r="H75">
-        <v>550</v>
-      </c>
-      <c r="I75" s="3">
-        <v>550</v>
+      <c r="F75">
+        <v>330</v>
+      </c>
+      <c r="G75" s="3">
+        <v>330</v>
+      </c>
+      <c r="I75">
+        <f>$AM$32</f>
+        <v>600</v>
       </c>
       <c r="K75">
         <f>$AM$39</f>
         <v>0.1</v>
       </c>
       <c r="M75">
-        <f t="shared" si="30"/>
+        <f t="shared" si="36"/>
         <v>1</v>
       </c>
       <c r="O75">
@@ -3694,24 +3719,28 @@
         <v>0</v>
       </c>
       <c r="Q75">
-        <f t="shared" si="29"/>
-        <v>8.5673290000000009</v>
+        <f t="shared" si="35"/>
+        <v>9.0270202499999979</v>
       </c>
       <c r="R75">
-        <f t="shared" si="31"/>
-        <v>0.17734371030000001</v>
+        <f t="shared" si="37"/>
+        <v>0.18685931917499995</v>
       </c>
       <c r="S75">
-        <f t="shared" si="32"/>
-        <v>2589.2181703800002</v>
+        <f t="shared" si="38"/>
+        <v>2466.5430131099993</v>
       </c>
       <c r="U75">
-        <f t="shared" si="34"/>
-        <v>0</v>
+        <f t="shared" si="41"/>
+        <v>0</v>
+      </c>
+      <c r="AC75">
+        <f t="shared" si="39"/>
+        <v>0.75</v>
       </c>
       <c r="AF75">
-        <f t="shared" si="33"/>
-        <v>2589.2181703800002</v>
+        <f t="shared" si="40"/>
+        <v>2466.5430131099993</v>
       </c>
     </row>
     <row r="76" spans="1:33" x14ac:dyDescent="0.2">
@@ -3727,21 +3756,22 @@
       <c r="E76">
         <v>30</v>
       </c>
-      <c r="G76">
-        <v>84</v>
-      </c>
-      <c r="H76">
-        <v>220</v>
-      </c>
-      <c r="I76" s="3">
-        <v>220</v>
+      <c r="F76">
+        <v>80</v>
+      </c>
+      <c r="G76" s="3">
+        <v>80</v>
+      </c>
+      <c r="I76">
+        <f>$AN$32</f>
+        <v>225</v>
       </c>
       <c r="K76">
         <f>$AM$40</f>
         <v>0.8</v>
       </c>
       <c r="M76">
-        <f t="shared" si="30"/>
+        <f t="shared" si="36"/>
         <v>1</v>
       </c>
       <c r="O76">
@@ -3751,28 +3781,24 @@
         <v>0</v>
       </c>
       <c r="Q76">
-        <f t="shared" si="29"/>
-        <v>5.3359152015999971</v>
-      </c>
-      <c r="R76">
-        <f t="shared" si="31"/>
-        <v>0.11045344467311993</v>
-      </c>
-      <c r="S76">
-        <f t="shared" si="32"/>
-        <v>278.34268057626224</v>
+        <f t="shared" si="35"/>
+        <v>5.4143472656250013</v>
       </c>
       <c r="T76">
         <f>$AM$51</f>
         <v>2.0400000000000001E-2</v>
       </c>
       <c r="U76">
-        <f t="shared" si="34"/>
-        <v>51.408000000000008</v>
+        <f t="shared" si="41"/>
+        <v>48.960000000000008</v>
+      </c>
+      <c r="AC76">
+        <f t="shared" si="39"/>
+        <v>0.75</v>
       </c>
       <c r="AF76">
-        <f t="shared" si="33"/>
-        <v>329.75068057626225</v>
+        <f t="shared" si="40"/>
+        <v>48.960000000000008</v>
       </c>
     </row>
     <row r="77" spans="1:33" x14ac:dyDescent="0.2">
@@ -3788,21 +3814,22 @@
       <c r="E77">
         <v>20</v>
       </c>
-      <c r="G77">
-        <v>281</v>
-      </c>
-      <c r="H77">
-        <v>230</v>
-      </c>
-      <c r="I77" s="3">
-        <v>230</v>
+      <c r="F77">
+        <v>285</v>
+      </c>
+      <c r="G77" s="3">
+        <v>285</v>
+      </c>
+      <c r="I77">
+        <f>$AN$32</f>
+        <v>225</v>
       </c>
       <c r="K77">
         <f>$AM$40</f>
         <v>0.8</v>
       </c>
       <c r="M77">
-        <f t="shared" si="30"/>
+        <f t="shared" si="36"/>
         <v>1</v>
       </c>
       <c r="O77">
@@ -3812,20 +3839,24 @@
         <v>0</v>
       </c>
       <c r="Q77">
-        <f t="shared" si="29"/>
-        <v>5.4927421955999991</v>
+        <f t="shared" si="35"/>
+        <v>5.4143472656250013</v>
       </c>
       <c r="R77">
-        <f t="shared" si="31"/>
-        <v>0.11369976344891998</v>
+        <f t="shared" si="37"/>
+        <v>0.11207698839843752</v>
       </c>
       <c r="S77">
-        <f t="shared" si="32"/>
-        <v>638.99267058293037</v>
+        <f t="shared" si="38"/>
+        <v>638.83883387109381</v>
+      </c>
+      <c r="AC77">
+        <f t="shared" si="39"/>
+        <v>0.75</v>
       </c>
       <c r="AF77">
-        <f t="shared" si="33"/>
-        <v>638.99267058293037</v>
+        <f t="shared" si="40"/>
+        <v>638.83883387109381</v>
       </c>
     </row>
     <row r="81" spans="1:33" x14ac:dyDescent="0.2">
@@ -3844,15 +3875,15 @@
       <c r="G81">
         <v>365</v>
       </c>
-      <c r="I81">
-        <f>VLOOKUP(C81,$AL$18:$AO$27, 2, FALSE)</f>
-        <v>650</v>
-      </c>
-      <c r="J81">
-        <v>0</v>
-      </c>
-      <c r="K81" s="3">
-        <v>0</v>
+      <c r="H81">
+        <v>620</v>
+      </c>
+      <c r="I81" s="3">
+        <v>620</v>
+      </c>
+      <c r="K81">
+        <f>$AM$36</f>
+        <v>1.6E-2</v>
       </c>
       <c r="M81">
         <f>$AM$45</f>
@@ -3866,16 +3897,16 @@
         <v>7.1849041227053947</v>
       </c>
       <c r="Q81">
-        <f t="shared" ref="Q81:Q87" si="35">(1.185 + 0.00454 *I81- 0.0000026 *I81^2 + 0.315 *K81)^2 *M81 + P81</f>
-        <v>17.333950997705397</v>
+        <f t="shared" ref="Q81:Q87" si="42">(1.185 + 0.00454 *I81- 0.0000026 *I81^2 + 0.315 *K81)^2 *M81 + P81</f>
+        <v>17.120576198705397</v>
       </c>
       <c r="R81">
         <f>20.7 * Q81 * 10^-3</f>
-        <v>0.35881278565250169</v>
+        <v>0.35439592731320169</v>
       </c>
       <c r="S81">
         <f>E81*R81*G81</f>
-        <v>6548.333338158156</v>
+        <v>6467.7256734659304</v>
       </c>
       <c r="W81">
         <f>$AN$12</f>
@@ -3907,11 +3938,11 @@
       </c>
       <c r="AF81">
         <f>S81+U81</f>
-        <v>6548.333338158156</v>
+        <v>6467.7256734659304</v>
       </c>
       <c r="AG81">
         <f>SUM(AF81:AF87)*10^-3</f>
-        <v>11.794633209792009</v>
+        <v>11.508309552978126</v>
       </c>
     </row>
     <row r="82" spans="1:33" x14ac:dyDescent="0.2">
@@ -3927,18 +3958,18 @@
       <c r="G82">
         <v>365</v>
       </c>
-      <c r="I82">
-        <f>VLOOKUP(C81,$AL$18:$AO$27, 3, FALSE)</f>
-        <v>450</v>
-      </c>
-      <c r="J82">
-        <v>0.2</v>
-      </c>
-      <c r="K82" s="3">
-        <v>0.2</v>
+      <c r="H82">
+        <v>440</v>
+      </c>
+      <c r="I82" s="3">
+        <v>440</v>
+      </c>
+      <c r="K82">
+        <f>$AM$37</f>
+        <v>0.6</v>
       </c>
       <c r="M82">
-        <f t="shared" ref="M82:M87" si="36">$AM$46</f>
+        <f t="shared" ref="M82:M87" si="43">$AM$46</f>
         <v>1</v>
       </c>
       <c r="O82">
@@ -3948,20 +3979,24 @@
         <v>0</v>
       </c>
       <c r="Q82">
-        <f t="shared" si="35"/>
-        <v>7.6424602500000001</v>
+        <f t="shared" si="42"/>
+        <v>8.2268006975999999</v>
       </c>
       <c r="R82">
-        <f t="shared" ref="R82:R87" si="37">20.7 * Q82 * 10^-3</f>
-        <v>0.158198927175</v>
+        <f t="shared" ref="R82:R87" si="44">20.7 * Q82 * 10^-3</f>
+        <v>0.17029477444032001</v>
       </c>
       <c r="S82">
-        <f t="shared" ref="S82:S87" si="38">E82*R82*G82</f>
-        <v>1154.8521683775</v>
+        <f t="shared" ref="S82:S87" si="45">E82*R82*G82</f>
+        <v>1243.1518534143361</v>
+      </c>
+      <c r="AC82">
+        <f t="shared" ref="AC82:AC87" si="46">$AN$8</f>
+        <v>0.75</v>
       </c>
       <c r="AF82">
-        <f t="shared" ref="AF82:AF87" si="39">S82+U82</f>
-        <v>1154.8521683775</v>
+        <f t="shared" ref="AF82:AF87" si="47">S82+U82</f>
+        <v>1243.1518534143361</v>
       </c>
     </row>
     <row r="83" spans="1:33" x14ac:dyDescent="0.2">
@@ -3980,18 +4015,18 @@
       <c r="G83">
         <v>84</v>
       </c>
-      <c r="I83">
-        <f>VLOOKUP(C81,$AL$18:$AO$27, 4, FALSE)</f>
-        <v>185</v>
-      </c>
-      <c r="J83">
-        <v>-0.1</v>
-      </c>
-      <c r="K83" s="3">
-        <v>-0.1</v>
+      <c r="H83">
+        <v>170</v>
+      </c>
+      <c r="I83" s="3">
+        <v>170</v>
+      </c>
+      <c r="K83">
+        <f>$AM$38</f>
+        <v>0.56999999999999995</v>
       </c>
       <c r="M83">
-        <f t="shared" si="36"/>
+        <f t="shared" si="43"/>
         <v>1</v>
       </c>
       <c r="O83">
@@ -4001,16 +4036,8 @@
         <v>0</v>
       </c>
       <c r="Q83">
-        <f t="shared" si="35"/>
-        <v>3.626796492225</v>
-      </c>
-      <c r="R83">
-        <f t="shared" si="37"/>
-        <v>7.5074687389057509E-2</v>
-      </c>
-      <c r="S83">
-        <f t="shared" si="38"/>
-        <v>63.06273740680831</v>
+        <f t="shared" si="42"/>
+        <v>4.2485866641000003</v>
       </c>
       <c r="T83">
         <f>$AM$50</f>
@@ -4020,9 +4047,13 @@
         <f>E83*T83*G83</f>
         <v>14.784000000000001</v>
       </c>
+      <c r="AC83">
+        <f t="shared" si="46"/>
+        <v>0.75</v>
+      </c>
       <c r="AF83">
-        <f t="shared" si="39"/>
-        <v>77.846737406808316</v>
+        <f t="shared" si="47"/>
+        <v>14.784000000000001</v>
       </c>
     </row>
     <row r="84" spans="1:33" x14ac:dyDescent="0.2">
@@ -4041,18 +4072,18 @@
       <c r="G84">
         <v>281</v>
       </c>
-      <c r="I84">
-        <f>VLOOKUP(C81,$AL$18:$AO$27, 4, FALSE)</f>
-        <v>185</v>
-      </c>
-      <c r="J84">
-        <v>0.6</v>
-      </c>
-      <c r="K84" s="3">
-        <v>0.6</v>
+      <c r="H84">
+        <v>175</v>
+      </c>
+      <c r="I84" s="3">
+        <v>175</v>
+      </c>
+      <c r="K84">
+        <f>$AM$38</f>
+        <v>0.56999999999999995</v>
       </c>
       <c r="M84">
-        <f t="shared" si="36"/>
+        <f t="shared" si="43"/>
         <v>1</v>
       </c>
       <c r="O84">
@@ -4062,24 +4093,28 @@
         <v>0</v>
       </c>
       <c r="Q84">
-        <f t="shared" si="35"/>
-        <v>4.5152637572250001</v>
+        <f t="shared" si="42"/>
+        <v>4.3240083306250003</v>
       </c>
       <c r="R84">
-        <f t="shared" si="37"/>
-        <v>9.3465959774557503E-2</v>
+        <f t="shared" si="44"/>
+        <v>8.9506972443937502E-2</v>
       </c>
       <c r="S84">
-        <f t="shared" si="38"/>
-        <v>525.27869393301319</v>
+        <f t="shared" si="45"/>
+        <v>503.02918513492875</v>
       </c>
       <c r="U84">
-        <f t="shared" ref="U84:U86" si="40">E84*T84*G84</f>
-        <v>0</v>
+        <f t="shared" ref="U84:U86" si="48">E84*T84*G84</f>
+        <v>0</v>
+      </c>
+      <c r="AC84">
+        <f t="shared" si="46"/>
+        <v>0.75</v>
       </c>
       <c r="AF84">
-        <f t="shared" si="39"/>
-        <v>525.27869393301319</v>
+        <f t="shared" si="47"/>
+        <v>503.02918513492875</v>
       </c>
     </row>
     <row r="85" spans="1:33" x14ac:dyDescent="0.2">
@@ -4095,18 +4130,18 @@
       <c r="G85">
         <v>365</v>
       </c>
-      <c r="I85">
-        <f>$AM$32</f>
-        <v>600</v>
-      </c>
-      <c r="J85">
-        <v>-0.2</v>
-      </c>
-      <c r="K85" s="3">
-        <v>-0.2</v>
+      <c r="H85">
+        <v>550</v>
+      </c>
+      <c r="I85" s="3">
+        <v>550</v>
+      </c>
+      <c r="K85">
+        <f>$AM$39</f>
+        <v>0.1</v>
       </c>
       <c r="M85">
-        <f t="shared" si="36"/>
+        <f t="shared" si="43"/>
         <v>1</v>
       </c>
       <c r="O85">
@@ -4116,24 +4151,28 @@
         <v>0</v>
       </c>
       <c r="Q85">
-        <f t="shared" si="35"/>
-        <v>8.468099999999998</v>
+        <f t="shared" si="42"/>
+        <v>8.5673290000000009</v>
       </c>
       <c r="R85">
-        <f t="shared" si="37"/>
-        <v>0.17528966999999995</v>
+        <f t="shared" si="44"/>
+        <v>0.17734371030000001</v>
       </c>
       <c r="S85">
-        <f t="shared" si="38"/>
-        <v>2559.2291819999991</v>
+        <f t="shared" si="45"/>
+        <v>2589.2181703800002</v>
       </c>
       <c r="U85">
-        <f t="shared" si="40"/>
-        <v>0</v>
+        <f t="shared" si="48"/>
+        <v>0</v>
+      </c>
+      <c r="AC85">
+        <f t="shared" si="46"/>
+        <v>0.75</v>
       </c>
       <c r="AF85">
-        <f t="shared" si="39"/>
-        <v>2559.2291819999991</v>
+        <f t="shared" si="47"/>
+        <v>2589.2181703800002</v>
       </c>
     </row>
     <row r="86" spans="1:33" x14ac:dyDescent="0.2">
@@ -4152,18 +4191,18 @@
       <c r="G86">
         <v>84</v>
       </c>
-      <c r="I86">
-        <f>$AN$32</f>
-        <v>225</v>
-      </c>
-      <c r="J86">
-        <v>1</v>
-      </c>
-      <c r="K86" s="3">
-        <v>1</v>
+      <c r="H86">
+        <v>220</v>
+      </c>
+      <c r="I86" s="3">
+        <v>220</v>
+      </c>
+      <c r="K86">
+        <f>$AM$40</f>
+        <v>0.8</v>
       </c>
       <c r="M86">
-        <f t="shared" si="36"/>
+        <f t="shared" si="43"/>
         <v>1</v>
       </c>
       <c r="O86">
@@ -4173,28 +4212,24 @@
         <v>0</v>
       </c>
       <c r="Q86">
-        <f t="shared" si="35"/>
-        <v>5.7115025156249999</v>
-      </c>
-      <c r="R86">
-        <f t="shared" si="37"/>
-        <v>0.11822810207343749</v>
-      </c>
-      <c r="S86">
-        <f t="shared" si="38"/>
-        <v>297.93481722506249</v>
+        <f t="shared" si="42"/>
+        <v>5.3359152015999971</v>
       </c>
       <c r="T86">
         <f>$AM$51</f>
         <v>2.0400000000000001E-2</v>
       </c>
       <c r="U86">
-        <f t="shared" si="40"/>
+        <f t="shared" si="48"/>
         <v>51.408000000000008</v>
       </c>
+      <c r="AC86">
+        <f t="shared" si="46"/>
+        <v>0.75</v>
+      </c>
       <c r="AF86">
-        <f t="shared" si="39"/>
-        <v>349.3428172250625</v>
+        <f t="shared" si="47"/>
+        <v>51.408000000000008</v>
       </c>
     </row>
     <row r="87" spans="1:33" x14ac:dyDescent="0.2">
@@ -4213,18 +4248,18 @@
       <c r="G87">
         <v>281</v>
       </c>
-      <c r="I87">
-        <f>$AN$32</f>
-        <v>225</v>
-      </c>
-      <c r="J87">
-        <v>0.5</v>
-      </c>
-      <c r="K87" s="3">
-        <v>0.5</v>
+      <c r="H87">
+        <v>230</v>
+      </c>
+      <c r="I87" s="3">
+        <v>230</v>
+      </c>
+      <c r="K87">
+        <f>$AM$40</f>
+        <v>0.8</v>
       </c>
       <c r="M87">
-        <f t="shared" si="36"/>
+        <f t="shared" si="43"/>
         <v>1</v>
       </c>
       <c r="O87">
@@ -4234,28 +4269,32 @@
         <v>0</v>
       </c>
       <c r="Q87">
-        <f t="shared" si="35"/>
-        <v>4.9834981406250014</v>
+        <f t="shared" si="42"/>
+        <v>5.4927421955999991</v>
       </c>
       <c r="R87">
-        <f t="shared" si="37"/>
-        <v>0.10315841151093753</v>
+        <f t="shared" si="44"/>
+        <v>0.11369976344891998</v>
       </c>
       <c r="S87">
-        <f t="shared" si="38"/>
-        <v>579.75027269146904</v>
+        <f t="shared" si="45"/>
+        <v>638.99267058293037</v>
+      </c>
+      <c r="AC87">
+        <f t="shared" si="46"/>
+        <v>0.75</v>
       </c>
       <c r="AF87">
-        <f t="shared" si="39"/>
-        <v>579.75027269146904</v>
+        <f t="shared" si="47"/>
+        <v>638.99267058293037</v>
       </c>
     </row>
     <row r="91" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="D91" t="s">
         <v>33</v>
@@ -4268,50 +4307,44 @@
       </c>
       <c r="I91">
         <f>VLOOKUP(C91,$AL$18:$AO$27, 2, FALSE)</f>
-        <v>550</v>
-      </c>
-      <c r="K91">
-        <f>$AM$36</f>
-        <v>1.6E-2</v>
+        <v>650</v>
+      </c>
+      <c r="J91">
+        <v>0</v>
+      </c>
+      <c r="K91" s="3">
+        <v>0</v>
       </c>
       <c r="M91">
         <f>$AM$45</f>
         <v>1.1000000000000001</v>
       </c>
-      <c r="N91" s="3">
-        <v>1.5</v>
-      </c>
       <c r="O91">
-        <f>N91/(0.01 * (W91+Y91))</f>
-        <v>24.193548387096772</v>
+        <v>15</v>
       </c>
       <c r="P91">
         <f>(O91 * 1.03 *AA91) / (Z91 * AE91 * AD91)</f>
-        <v>11.588555036621603</v>
+        <v>7.1849041227053947</v>
       </c>
       <c r="Q91">
-        <f t="shared" ref="Q91:Q97" si="41">(1.185 + 0.00454 *I91- 0.0000026 *I91^2 + 0.315 *K91)^2 *M91 + P91</f>
-        <v>20.843000557381608</v>
+        <f t="shared" ref="Q91:Q97" si="49">(1.185 + 0.00454 *I91- 0.0000026 *I91^2 + 0.315 *K91)^2 *M91 + P91</f>
+        <v>17.333950997705397</v>
       </c>
       <c r="R91">
         <f>20.7 * Q91 * 10^-3</f>
-        <v>0.43145011153779927</v>
+        <v>0.35881278565250169</v>
       </c>
       <c r="S91">
         <f>E91*R91*G91</f>
-        <v>7873.9645355648363</v>
-      </c>
-      <c r="V91" s="3">
-        <v>3.5</v>
-      </c>
-      <c r="W91" s="3">
-        <v>3.5</v>
-      </c>
-      <c r="X91" s="3">
-        <v>2.7</v>
-      </c>
-      <c r="Y91" s="3">
-        <v>2.7</v>
+        <v>6548.333338158156</v>
+      </c>
+      <c r="W91">
+        <f>$AN$12</f>
+        <v>4</v>
+      </c>
+      <c r="Y91">
+        <f>$AN$11</f>
+        <v>3.3</v>
       </c>
       <c r="Z91">
         <f>$AN$10</f>
@@ -4335,11 +4368,11 @@
       </c>
       <c r="AF91">
         <f>S91+U91</f>
-        <v>7873.9645355648363</v>
+        <v>6548.333338158156</v>
       </c>
       <c r="AG91">
         <f>SUM(AF91:AF97)*10^-3</f>
-        <v>13.219076612865418</v>
+        <v>11.433635655160135</v>
       </c>
     </row>
     <row r="92" spans="1:33" x14ac:dyDescent="0.2">
@@ -4357,14 +4390,16 @@
       </c>
       <c r="I92">
         <f>VLOOKUP(C91,$AL$18:$AO$27, 3, FALSE)</f>
-        <v>375</v>
-      </c>
-      <c r="K92">
-        <f>$AM$37</f>
-        <v>0.6</v>
+        <v>450</v>
+      </c>
+      <c r="J92">
+        <v>0.2</v>
+      </c>
+      <c r="K92" s="3">
+        <v>0.2</v>
       </c>
       <c r="M92">
-        <f t="shared" ref="M92:M97" si="42">$AM$46</f>
+        <f t="shared" ref="M92:M97" si="50">$AM$46</f>
         <v>1</v>
       </c>
       <c r="O92">
@@ -4374,20 +4409,24 @@
         <v>0</v>
       </c>
       <c r="Q92">
-        <f t="shared" si="41"/>
-        <v>7.3488432656250007</v>
+        <f t="shared" si="49"/>
+        <v>7.6424602500000001</v>
       </c>
       <c r="R92">
-        <f t="shared" ref="R92:R97" si="43">20.7 * Q92 * 10^-3</f>
-        <v>0.15212105559843753</v>
+        <f t="shared" ref="R92:R97" si="51">20.7 * Q92 * 10^-3</f>
+        <v>0.158198927175</v>
       </c>
       <c r="S92">
-        <f t="shared" ref="S92:S97" si="44">E92*R92*G92</f>
-        <v>1110.4837058685939</v>
+        <f t="shared" ref="S92:S97" si="52">E92*R92*G92</f>
+        <v>1154.8521683775</v>
+      </c>
+      <c r="AC92">
+        <f t="shared" ref="AC92:AC97" si="53">$AN$8</f>
+        <v>0.75</v>
       </c>
       <c r="AF92">
-        <f t="shared" ref="AF92:AF97" si="45">S92+U92</f>
-        <v>1110.4837058685939</v>
+        <f t="shared" ref="AF92:AF97" si="54">S92+U92</f>
+        <v>1154.8521683775</v>
       </c>
     </row>
     <row r="93" spans="1:33" x14ac:dyDescent="0.2">
@@ -4408,14 +4447,16 @@
       </c>
       <c r="I93">
         <f>VLOOKUP(C91,$AL$18:$AO$27, 4, FALSE)</f>
-        <v>150</v>
-      </c>
-      <c r="K93">
-        <f>$AM$38</f>
-        <v>0.56999999999999995</v>
+        <v>185</v>
+      </c>
+      <c r="J93">
+        <v>-0.1</v>
+      </c>
+      <c r="K93" s="3">
+        <v>-0.1</v>
       </c>
       <c r="M93">
-        <f t="shared" si="42"/>
+        <f t="shared" si="50"/>
         <v>1</v>
       </c>
       <c r="O93">
@@ -4425,16 +4466,8 @@
         <v>0</v>
       </c>
       <c r="Q93">
-        <f t="shared" si="41"/>
-        <v>3.9483677025000001</v>
-      </c>
-      <c r="R93">
-        <f t="shared" si="43"/>
-        <v>8.173121144175001E-2</v>
-      </c>
-      <c r="S93">
-        <f t="shared" si="44"/>
-        <v>68.65421761107001</v>
+        <f t="shared" si="49"/>
+        <v>3.626796492225</v>
       </c>
       <c r="T93">
         <f>$AM$50</f>
@@ -4444,9 +4477,13 @@
         <f>E93*T93*G93</f>
         <v>14.784000000000001</v>
       </c>
+      <c r="AC93">
+        <f t="shared" si="53"/>
+        <v>0.75</v>
+      </c>
       <c r="AF93">
-        <f t="shared" si="45"/>
-        <v>83.438217611070016</v>
+        <f t="shared" si="54"/>
+        <v>14.784000000000001</v>
       </c>
     </row>
     <row r="94" spans="1:33" x14ac:dyDescent="0.2">
@@ -4467,14 +4504,16 @@
       </c>
       <c r="I94">
         <f>VLOOKUP(C91,$AL$18:$AO$27, 4, FALSE)</f>
-        <v>150</v>
-      </c>
-      <c r="K94">
-        <f>$AM$38</f>
-        <v>0.56999999999999995</v>
+        <v>185</v>
+      </c>
+      <c r="J94">
+        <v>0.6</v>
+      </c>
+      <c r="K94" s="3">
+        <v>0.6</v>
       </c>
       <c r="M94">
-        <f t="shared" si="42"/>
+        <f t="shared" si="50"/>
         <v>1</v>
       </c>
       <c r="O94">
@@ -4484,24 +4523,28 @@
         <v>0</v>
       </c>
       <c r="Q94">
-        <f t="shared" si="41"/>
-        <v>3.9483677025000001</v>
+        <f t="shared" si="49"/>
+        <v>4.5152637572250001</v>
       </c>
       <c r="R94">
-        <f t="shared" si="43"/>
-        <v>8.173121144175001E-2</v>
+        <f t="shared" si="51"/>
+        <v>9.3465959774557503E-2</v>
       </c>
       <c r="S94">
-        <f t="shared" si="44"/>
-        <v>459.32940830263504</v>
+        <f t="shared" si="52"/>
+        <v>525.27869393301319</v>
       </c>
       <c r="U94">
-        <f t="shared" ref="U94:U96" si="46">E94*T94*G94</f>
-        <v>0</v>
+        <f t="shared" ref="U94:U96" si="55">E94*T94*G94</f>
+        <v>0</v>
+      </c>
+      <c r="AC94">
+        <f t="shared" si="53"/>
+        <v>0.75</v>
       </c>
       <c r="AF94">
-        <f t="shared" si="45"/>
-        <v>459.32940830263504</v>
+        <f t="shared" si="54"/>
+        <v>525.27869393301319</v>
       </c>
     </row>
     <row r="95" spans="1:33" x14ac:dyDescent="0.2">
@@ -4521,12 +4564,14 @@
         <f>$AM$32</f>
         <v>600</v>
       </c>
-      <c r="K95">
-        <f>$AM$39</f>
-        <v>0.1</v>
+      <c r="J95">
+        <v>-0.2</v>
+      </c>
+      <c r="K95" s="3">
+        <v>-0.2</v>
       </c>
       <c r="M95">
-        <f t="shared" si="42"/>
+        <f t="shared" si="50"/>
         <v>1</v>
       </c>
       <c r="O95">
@@ -4536,24 +4581,28 @@
         <v>0</v>
       </c>
       <c r="Q95">
-        <f t="shared" si="41"/>
-        <v>9.0270202499999979</v>
+        <f t="shared" si="49"/>
+        <v>8.468099999999998</v>
       </c>
       <c r="R95">
-        <f t="shared" si="43"/>
-        <v>0.18685931917499995</v>
+        <f t="shared" si="51"/>
+        <v>0.17528966999999995</v>
       </c>
       <c r="S95">
-        <f t="shared" si="44"/>
-        <v>2728.1460599549996</v>
+        <f t="shared" si="52"/>
+        <v>2559.2291819999991</v>
       </c>
       <c r="U95">
-        <f t="shared" si="46"/>
-        <v>0</v>
+        <f t="shared" si="55"/>
+        <v>0</v>
+      </c>
+      <c r="AC95">
+        <f t="shared" si="53"/>
+        <v>0.75</v>
       </c>
       <c r="AF95">
-        <f t="shared" si="45"/>
-        <v>2728.1460599549996</v>
+        <f t="shared" si="54"/>
+        <v>2559.2291819999991</v>
       </c>
     </row>
     <row r="96" spans="1:33" x14ac:dyDescent="0.2">
@@ -4576,12 +4625,14 @@
         <f>$AN$32</f>
         <v>225</v>
       </c>
-      <c r="K96">
-        <f>$AM$40</f>
-        <v>0.8</v>
+      <c r="J96">
+        <v>1</v>
+      </c>
+      <c r="K96" s="3">
+        <v>1</v>
       </c>
       <c r="M96">
-        <f t="shared" si="42"/>
+        <f t="shared" si="50"/>
         <v>1</v>
       </c>
       <c r="O96">
@@ -4591,28 +4642,24 @@
         <v>0</v>
       </c>
       <c r="Q96">
-        <f t="shared" si="41"/>
-        <v>5.4143472656250013</v>
-      </c>
-      <c r="R96">
-        <f t="shared" si="43"/>
-        <v>0.11207698839843752</v>
-      </c>
-      <c r="S96">
-        <f t="shared" si="44"/>
-        <v>282.43401076406252</v>
+        <f t="shared" si="49"/>
+        <v>5.7115025156249999</v>
       </c>
       <c r="T96">
         <f>$AM$51</f>
         <v>2.0400000000000001E-2</v>
       </c>
       <c r="U96">
-        <f t="shared" si="46"/>
+        <f t="shared" si="55"/>
         <v>51.408000000000008</v>
       </c>
+      <c r="AC96">
+        <f t="shared" si="53"/>
+        <v>0.75</v>
+      </c>
       <c r="AF96">
-        <f t="shared" si="45"/>
-        <v>333.84201076406254</v>
+        <f t="shared" si="54"/>
+        <v>51.408000000000008</v>
       </c>
     </row>
     <row r="97" spans="1:33" x14ac:dyDescent="0.2">
@@ -4635,12 +4682,14 @@
         <f>$AN$32</f>
         <v>225</v>
       </c>
-      <c r="K97">
-        <f>$AM$40</f>
-        <v>0.8</v>
+      <c r="J97">
+        <v>0.5</v>
+      </c>
+      <c r="K97" s="3">
+        <v>0.5</v>
       </c>
       <c r="M97">
-        <f t="shared" si="42"/>
+        <f t="shared" si="50"/>
         <v>1</v>
       </c>
       <c r="O97">
@@ -4650,20 +4699,24 @@
         <v>0</v>
       </c>
       <c r="Q97">
-        <f t="shared" si="41"/>
-        <v>5.4143472656250013</v>
+        <f t="shared" si="49"/>
+        <v>4.9834981406250014</v>
       </c>
       <c r="R97">
-        <f t="shared" si="43"/>
-        <v>0.11207698839843752</v>
+        <f t="shared" si="51"/>
+        <v>0.10315841151093753</v>
       </c>
       <c r="S97">
-        <f t="shared" si="44"/>
-        <v>629.87267479921888</v>
+        <f t="shared" si="52"/>
+        <v>579.75027269146904</v>
+      </c>
+      <c r="AC97">
+        <f t="shared" si="53"/>
+        <v>0.75</v>
       </c>
       <c r="AF97">
-        <f t="shared" si="45"/>
-        <v>629.87267479921888</v>
+        <f t="shared" si="54"/>
+        <v>579.75027269146904</v>
       </c>
     </row>
     <row r="101" spans="1:33" x14ac:dyDescent="0.2">
@@ -4671,7 +4724,7 @@
         <v>88</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D101" t="s">
         <v>33</v>
@@ -4684,7 +4737,7 @@
       </c>
       <c r="I101">
         <f>VLOOKUP(C101,$AL$18:$AO$27, 2, FALSE)</f>
-        <v>540</v>
+        <v>550</v>
       </c>
       <c r="K101">
         <f>$AM$36</f>
@@ -4694,32 +4747,40 @@
         <f>$AM$45</f>
         <v>1.1000000000000001</v>
       </c>
+      <c r="N101" s="3">
+        <v>1.5</v>
+      </c>
       <c r="O101">
-        <v>12</v>
+        <f>N101/(0.01 * (W101+Y101))</f>
+        <v>24.193548387096772</v>
       </c>
       <c r="P101">
         <f>(O101 * 1.03 *AA101) / (Z101 * AE101 * AD101)</f>
-        <v>3.3128109426538548</v>
+        <v>11.588555036621603</v>
       </c>
       <c r="Q101">
-        <f t="shared" ref="Q101:Q107" si="47">(1.185 + 0.00454 *I101- 0.0000026 *I101^2 + 0.315 *K101)^2 *M101 + P101</f>
-        <v>12.458713544093856</v>
+        <f t="shared" ref="Q101:Q107" si="56">(1.185 + 0.00454 *I101- 0.0000026 *I101^2 + 0.315 *K101)^2 *M101 + P101</f>
+        <v>20.843000557381608</v>
       </c>
       <c r="R101">
         <f>20.7 * Q101 * 10^-3</f>
-        <v>0.25789537036274285</v>
+        <v>0.43145011153779927</v>
       </c>
       <c r="S101">
         <f>E101*R101*G101</f>
-        <v>4706.5905091200575</v>
-      </c>
-      <c r="W101">
-        <f>$AN$12</f>
-        <v>4</v>
-      </c>
-      <c r="Y101">
-        <f>$AN$11</f>
-        <v>3.3</v>
+        <v>7873.9645355648363</v>
+      </c>
+      <c r="V101" s="3">
+        <v>3.5</v>
+      </c>
+      <c r="W101" s="3">
+        <v>3.5</v>
+      </c>
+      <c r="X101" s="3">
+        <v>2.7</v>
+      </c>
+      <c r="Y101" s="3">
+        <v>2.7</v>
       </c>
       <c r="Z101">
         <f>$AN$10</f>
@@ -4729,15 +4790,13 @@
         <f>$AN$13</f>
         <v>3.0539999999999998</v>
       </c>
-      <c r="AB101" s="3">
-        <v>1.3</v>
-      </c>
-      <c r="AC101" s="3">
-        <v>1.3</v>
+      <c r="AC101">
+        <f>$AN$8</f>
+        <v>0.75</v>
       </c>
       <c r="AD101">
         <f>0.795 * AC101- 0.0014</f>
-        <v>1.0321</v>
+        <v>0.5948500000000001</v>
       </c>
       <c r="AE101">
         <f>$AN$9</f>
@@ -4745,18 +4804,17 @@
       </c>
       <c r="AF101">
         <f>S101+U101</f>
-        <v>4706.5905091200575</v>
+        <v>7873.9645355648363</v>
       </c>
       <c r="AG101">
         <f>SUM(AF101:AF107)*10^-3</f>
-        <v>10.051702586420639</v>
+        <v>12.867988384490284</v>
       </c>
     </row>
     <row r="102" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A102">
         <v>2</v>
       </c>
-      <c r="C102" s="2"/>
       <c r="D102" t="s">
         <v>34</v>
       </c>
@@ -4775,7 +4833,7 @@
         <v>0.6</v>
       </c>
       <c r="M102">
-        <f t="shared" ref="M102:M107" si="48">$AM$46</f>
+        <f t="shared" ref="M102:M107" si="57">$AM$46</f>
         <v>1</v>
       </c>
       <c r="O102">
@@ -4785,19 +4843,23 @@
         <v>0</v>
       </c>
       <c r="Q102">
-        <f t="shared" si="47"/>
+        <f t="shared" si="56"/>
         <v>7.3488432656250007</v>
       </c>
       <c r="R102">
-        <f t="shared" ref="R102:R107" si="49">20.7 * Q102 * 10^-3</f>
+        <f t="shared" ref="R102:R107" si="58">20.7 * Q102 * 10^-3</f>
         <v>0.15212105559843753</v>
       </c>
       <c r="S102">
-        <f t="shared" ref="S102:S107" si="50">E102*R102*G102</f>
+        <f t="shared" ref="S102:S107" si="59">E102*R102*G102</f>
         <v>1110.4837058685939</v>
       </c>
+      <c r="AC102">
+        <f t="shared" ref="AC102:AC107" si="60">$AN$8</f>
+        <v>0.75</v>
+      </c>
       <c r="AF102">
-        <f t="shared" ref="AF102:AF107" si="51">S102+U102</f>
+        <f t="shared" ref="AF102:AF107" si="61">S102+U102</f>
         <v>1110.4837058685939</v>
       </c>
     </row>
@@ -4826,7 +4888,7 @@
         <v>0.56999999999999995</v>
       </c>
       <c r="M103">
-        <f t="shared" si="48"/>
+        <f t="shared" si="57"/>
         <v>1</v>
       </c>
       <c r="O103">
@@ -4836,16 +4898,8 @@
         <v>0</v>
       </c>
       <c r="Q103">
-        <f t="shared" si="47"/>
+        <f t="shared" si="56"/>
         <v>3.9483677025000001</v>
-      </c>
-      <c r="R103">
-        <f t="shared" si="49"/>
-        <v>8.173121144175001E-2</v>
-      </c>
-      <c r="S103">
-        <f t="shared" si="50"/>
-        <v>68.65421761107001</v>
       </c>
       <c r="T103">
         <f>$AM$50</f>
@@ -4855,9 +4909,13 @@
         <f>E103*T103*G103</f>
         <v>14.784000000000001</v>
       </c>
+      <c r="AC103">
+        <f t="shared" si="60"/>
+        <v>0.75</v>
+      </c>
       <c r="AF103">
-        <f t="shared" si="51"/>
-        <v>83.438217611070016</v>
+        <f t="shared" si="61"/>
+        <v>14.784000000000001</v>
       </c>
     </row>
     <row r="104" spans="1:33" x14ac:dyDescent="0.2">
@@ -4885,7 +4943,7 @@
         <v>0.56999999999999995</v>
       </c>
       <c r="M104">
-        <f t="shared" si="48"/>
+        <f t="shared" si="57"/>
         <v>1</v>
       </c>
       <c r="O104">
@@ -4895,23 +4953,27 @@
         <v>0</v>
       </c>
       <c r="Q104">
-        <f t="shared" si="47"/>
+        <f t="shared" si="56"/>
         <v>3.9483677025000001</v>
       </c>
       <c r="R104">
-        <f t="shared" si="49"/>
+        <f t="shared" si="58"/>
         <v>8.173121144175001E-2</v>
       </c>
       <c r="S104">
-        <f t="shared" si="50"/>
+        <f t="shared" si="59"/>
         <v>459.32940830263504</v>
       </c>
       <c r="U104">
-        <f t="shared" ref="U104:U106" si="52">E104*T104*G104</f>
-        <v>0</v>
+        <f t="shared" ref="U104:U106" si="62">E104*T104*G104</f>
+        <v>0</v>
+      </c>
+      <c r="AC104">
+        <f t="shared" si="60"/>
+        <v>0.75</v>
       </c>
       <c r="AF104">
-        <f t="shared" si="51"/>
+        <f t="shared" si="61"/>
         <v>459.32940830263504</v>
       </c>
     </row>
@@ -4937,7 +4999,7 @@
         <v>0.1</v>
       </c>
       <c r="M105">
-        <f t="shared" si="48"/>
+        <f t="shared" si="57"/>
         <v>1</v>
       </c>
       <c r="O105">
@@ -4947,23 +5009,27 @@
         <v>0</v>
       </c>
       <c r="Q105">
-        <f t="shared" si="47"/>
+        <f t="shared" si="56"/>
         <v>9.0270202499999979</v>
       </c>
       <c r="R105">
-        <f t="shared" si="49"/>
+        <f t="shared" si="58"/>
         <v>0.18685931917499995</v>
       </c>
       <c r="S105">
-        <f t="shared" si="50"/>
+        <f t="shared" si="59"/>
         <v>2728.1460599549996</v>
       </c>
       <c r="U105">
-        <f t="shared" si="52"/>
-        <v>0</v>
+        <f t="shared" si="62"/>
+        <v>0</v>
+      </c>
+      <c r="AC105">
+        <f t="shared" si="60"/>
+        <v>0.75</v>
       </c>
       <c r="AF105">
-        <f t="shared" si="51"/>
+        <f t="shared" si="61"/>
         <v>2728.1460599549996</v>
       </c>
     </row>
@@ -4992,7 +5058,7 @@
         <v>0.8</v>
       </c>
       <c r="M106">
-        <f t="shared" si="48"/>
+        <f t="shared" si="57"/>
         <v>1</v>
       </c>
       <c r="O106">
@@ -5002,28 +5068,24 @@
         <v>0</v>
       </c>
       <c r="Q106">
-        <f t="shared" si="47"/>
+        <f t="shared" si="56"/>
         <v>5.4143472656250013</v>
-      </c>
-      <c r="R106">
-        <f t="shared" si="49"/>
-        <v>0.11207698839843752</v>
-      </c>
-      <c r="S106">
-        <f t="shared" si="50"/>
-        <v>282.43401076406252</v>
       </c>
       <c r="T106">
         <f>$AM$51</f>
         <v>2.0400000000000001E-2</v>
       </c>
       <c r="U106">
-        <f t="shared" si="52"/>
+        <f t="shared" si="62"/>
         <v>51.408000000000008</v>
       </c>
+      <c r="AC106">
+        <f t="shared" si="60"/>
+        <v>0.75</v>
+      </c>
       <c r="AF106">
-        <f t="shared" si="51"/>
-        <v>333.84201076406254</v>
+        <f t="shared" si="61"/>
+        <v>51.408000000000008</v>
       </c>
     </row>
     <row r="107" spans="1:33" x14ac:dyDescent="0.2">
@@ -5051,7 +5113,7 @@
         <v>0.8</v>
       </c>
       <c r="M107">
-        <f t="shared" si="48"/>
+        <f t="shared" si="57"/>
         <v>1</v>
       </c>
       <c r="O107">
@@ -5061,31 +5123,32 @@
         <v>0</v>
       </c>
       <c r="Q107">
-        <f t="shared" si="47"/>
+        <f t="shared" si="56"/>
         <v>5.4143472656250013</v>
       </c>
       <c r="R107">
-        <f t="shared" si="49"/>
+        <f t="shared" si="58"/>
         <v>0.11207698839843752</v>
       </c>
       <c r="S107">
-        <f t="shared" si="50"/>
+        <f t="shared" si="59"/>
         <v>629.87267479921888</v>
       </c>
+      <c r="AC107">
+        <f t="shared" si="60"/>
+        <v>0.75</v>
+      </c>
       <c r="AF107">
-        <f t="shared" si="51"/>
+        <f t="shared" si="61"/>
         <v>629.87267479921888</v>
       </c>
-    </row>
-    <row r="110" spans="1:33" x14ac:dyDescent="0.2">
-      <c r="C110" s="2"/>
     </row>
     <row r="111" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>88</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D111" t="s">
         <v>33</v>
@@ -5098,7 +5161,7 @@
       </c>
       <c r="I111">
         <f>VLOOKUP(C111,$AL$18:$AO$27, 2, FALSE)</f>
-        <v>480</v>
+        <v>540</v>
       </c>
       <c r="K111">
         <f>$AM$36</f>
@@ -5109,23 +5172,23 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="O111">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="P111">
         <f>(O111 * 1.03 *AA111) / (Z111 * AE111 * AD111)</f>
-        <v>4.7899360818035959</v>
+        <v>3.3128109426538548</v>
       </c>
       <c r="Q111">
-        <f t="shared" ref="Q111:Q117" si="53">(1.185 + 0.00454 *I111- 0.0000026 *I111^2 + 0.315 *K111)^2 *M111 + P111</f>
-        <v>13.231344925803597</v>
+        <f t="shared" ref="Q111:Q117" si="63">(1.185 + 0.00454 *I111- 0.0000026 *I111^2 + 0.315 *K111)^2 *M111 + P111</f>
+        <v>12.458713544093856</v>
       </c>
       <c r="R111">
         <f>20.7 * Q111 * 10^-3</f>
-        <v>0.27388883996413443</v>
+        <v>0.25789537036274285</v>
       </c>
       <c r="S111">
         <f>E111*R111*G111</f>
-        <v>4998.4713293454533</v>
+        <v>4706.5905091200575</v>
       </c>
       <c r="W111">
         <f>$AN$12</f>
@@ -5143,13 +5206,15 @@
         <f>$AN$13</f>
         <v>3.0539999999999998</v>
       </c>
-      <c r="AC111">
-        <f>$AN$8</f>
-        <v>0.75</v>
+      <c r="AB111" s="3">
+        <v>1.3</v>
+      </c>
+      <c r="AC111" s="3">
+        <v>1.3</v>
       </c>
       <c r="AD111">
         <f>0.795 * AC111- 0.0014</f>
-        <v>0.5948500000000001</v>
+        <v>1.0321</v>
       </c>
       <c r="AE111">
         <f>$AN$9</f>
@@ -5157,17 +5222,18 @@
       </c>
       <c r="AF111">
         <f>S111+U111</f>
-        <v>4998.4713293454533</v>
+        <v>4706.5905091200575</v>
       </c>
       <c r="AG111">
         <f>SUM(AF111:AF117)*10^-3</f>
-        <v>10.237124385835068</v>
+        <v>9.7006143580455042</v>
       </c>
     </row>
     <row r="112" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A112">
         <v>2</v>
       </c>
+      <c r="C112" s="2"/>
       <c r="D112" t="s">
         <v>34</v>
       </c>
@@ -5179,14 +5245,14 @@
       </c>
       <c r="I112">
         <f>VLOOKUP(C111,$AL$18:$AO$27, 3, FALSE)</f>
-        <v>335</v>
+        <v>375</v>
       </c>
       <c r="K112">
         <f>$AM$37</f>
         <v>0.6</v>
       </c>
       <c r="M112">
-        <f t="shared" ref="M112:M117" si="54">$AM$46</f>
+        <f t="shared" ref="M112:M117" si="64">$AM$46</f>
         <v>1</v>
       </c>
       <c r="O112">
@@ -5196,20 +5262,26 @@
         <v>0</v>
       </c>
       <c r="Q112">
-        <f t="shared" si="53"/>
-        <v>6.7762077032249994</v>
+        <f t="shared" si="63"/>
+        <v>7.3488432656250007</v>
       </c>
       <c r="R112">
-        <f t="shared" ref="R112:R117" si="55">20.7 * Q112 * 10^-3</f>
-        <v>0.14026749945675748</v>
+        <f t="shared" ref="R112:R117" si="65">20.7 * Q112 * 10^-3</f>
+        <v>0.15212105559843753</v>
       </c>
       <c r="S112">
-        <f t="shared" ref="S112:S117" si="56">E112*R112*G112</f>
-        <v>1023.9527460343295</v>
+        <f t="shared" ref="S112:S117" si="66">E112*R112*G112</f>
+        <v>1110.4837058685939</v>
+      </c>
+      <c r="AB112" s="3">
+        <v>1.3</v>
+      </c>
+      <c r="AC112" s="3">
+        <v>1.3</v>
       </c>
       <c r="AF112">
-        <f t="shared" ref="AF112:AF117" si="57">S112+U112</f>
-        <v>1023.9527460343295</v>
+        <f t="shared" ref="AF112:AF117" si="67">S112+U112</f>
+        <v>1110.4837058685939</v>
       </c>
     </row>
     <row r="113" spans="1:32" x14ac:dyDescent="0.2">
@@ -5230,14 +5302,14 @@
       </c>
       <c r="I113">
         <f>VLOOKUP(C111,$AL$18:$AO$27, 4, FALSE)</f>
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="K113">
         <f>$AM$38</f>
         <v>0.56999999999999995</v>
       </c>
       <c r="M113">
-        <f t="shared" si="54"/>
+        <f t="shared" si="64"/>
         <v>1</v>
       </c>
       <c r="O113">
@@ -5247,16 +5319,8 @@
         <v>0</v>
       </c>
       <c r="Q113">
-        <f t="shared" si="53"/>
-        <v>3.7993416560999989</v>
-      </c>
-      <c r="R113">
-        <f t="shared" si="55"/>
-        <v>7.8646372281269972E-2</v>
-      </c>
-      <c r="S113">
-        <f t="shared" si="56"/>
-        <v>66.062952716266778</v>
+        <f t="shared" si="63"/>
+        <v>3.9483677025000001</v>
       </c>
       <c r="T113">
         <f>$AM$50</f>
@@ -5266,9 +5330,15 @@
         <f>E113*T113*G113</f>
         <v>14.784000000000001</v>
       </c>
+      <c r="AB113" s="3">
+        <v>1.3</v>
+      </c>
+      <c r="AC113" s="3">
+        <v>1.3</v>
+      </c>
       <c r="AF113">
-        <f t="shared" si="57"/>
-        <v>80.846952716266784</v>
+        <f t="shared" si="67"/>
+        <v>14.784000000000001</v>
       </c>
     </row>
     <row r="114" spans="1:32" x14ac:dyDescent="0.2">
@@ -5289,14 +5359,14 @@
       </c>
       <c r="I114">
         <f>VLOOKUP(C111,$AL$18:$AO$27, 4, FALSE)</f>
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="K114">
         <f>$AM$38</f>
         <v>0.56999999999999995</v>
       </c>
       <c r="M114">
-        <f t="shared" si="54"/>
+        <f t="shared" si="64"/>
         <v>1</v>
       </c>
       <c r="O114">
@@ -5306,24 +5376,30 @@
         <v>0</v>
       </c>
       <c r="Q114">
-        <f t="shared" si="53"/>
-        <v>3.7993416560999989</v>
+        <f t="shared" si="63"/>
+        <v>3.9483677025000001</v>
       </c>
       <c r="R114">
-        <f t="shared" si="55"/>
-        <v>7.8646372281269972E-2</v>
+        <f t="shared" si="65"/>
+        <v>8.173121144175001E-2</v>
       </c>
       <c r="S114">
-        <f t="shared" si="56"/>
-        <v>441.99261222073721</v>
+        <f t="shared" si="66"/>
+        <v>459.32940830263504</v>
       </c>
       <c r="U114">
-        <f t="shared" ref="U114:U116" si="58">E114*T114*G114</f>
-        <v>0</v>
+        <f t="shared" ref="U114:U116" si="68">E114*T114*G114</f>
+        <v>0</v>
+      </c>
+      <c r="AB114" s="3">
+        <v>1.3</v>
+      </c>
+      <c r="AC114" s="3">
+        <v>1.3</v>
       </c>
       <c r="AF114">
-        <f t="shared" si="57"/>
-        <v>441.99261222073721</v>
+        <f t="shared" si="67"/>
+        <v>459.32940830263504</v>
       </c>
     </row>
     <row r="115" spans="1:32" x14ac:dyDescent="0.2">
@@ -5348,7 +5424,7 @@
         <v>0.1</v>
       </c>
       <c r="M115">
-        <f t="shared" si="54"/>
+        <f t="shared" si="64"/>
         <v>1</v>
       </c>
       <c r="O115">
@@ -5358,23 +5434,29 @@
         <v>0</v>
       </c>
       <c r="Q115">
-        <f t="shared" si="53"/>
+        <f t="shared" si="63"/>
         <v>9.0270202499999979</v>
       </c>
       <c r="R115">
-        <f t="shared" si="55"/>
+        <f t="shared" si="65"/>
         <v>0.18685931917499995</v>
       </c>
       <c r="S115">
-        <f t="shared" si="56"/>
+        <f t="shared" si="66"/>
         <v>2728.1460599549996</v>
       </c>
       <c r="U115">
-        <f t="shared" si="58"/>
-        <v>0</v>
+        <f t="shared" si="68"/>
+        <v>0</v>
+      </c>
+      <c r="AB115" s="3">
+        <v>1.3</v>
+      </c>
+      <c r="AC115" s="3">
+        <v>1.3</v>
       </c>
       <c r="AF115">
-        <f t="shared" si="57"/>
+        <f t="shared" si="67"/>
         <v>2728.1460599549996</v>
       </c>
     </row>
@@ -5403,7 +5485,7 @@
         <v>0.8</v>
       </c>
       <c r="M116">
-        <f t="shared" si="54"/>
+        <f t="shared" si="64"/>
         <v>1</v>
       </c>
       <c r="O116">
@@ -5413,28 +5495,26 @@
         <v>0</v>
       </c>
       <c r="Q116">
-        <f t="shared" si="53"/>
+        <f t="shared" si="63"/>
         <v>5.4143472656250013</v>
-      </c>
-      <c r="R116">
-        <f t="shared" si="55"/>
-        <v>0.11207698839843752</v>
-      </c>
-      <c r="S116">
-        <f t="shared" si="56"/>
-        <v>282.43401076406252</v>
       </c>
       <c r="T116">
         <f>$AM$51</f>
         <v>2.0400000000000001E-2</v>
       </c>
       <c r="U116">
-        <f t="shared" si="58"/>
+        <f t="shared" si="68"/>
         <v>51.408000000000008</v>
       </c>
+      <c r="AB116" s="3">
+        <v>1.3</v>
+      </c>
+      <c r="AC116" s="3">
+        <v>1.3</v>
+      </c>
       <c r="AF116">
-        <f t="shared" si="57"/>
-        <v>333.84201076406254</v>
+        <f t="shared" si="67"/>
+        <v>51.408000000000008</v>
       </c>
     </row>
     <row r="117" spans="1:32" x14ac:dyDescent="0.2">
@@ -5462,7 +5542,7 @@
         <v>0.8</v>
       </c>
       <c r="M117">
-        <f t="shared" si="54"/>
+        <f t="shared" si="64"/>
         <v>1</v>
       </c>
       <c r="O117">
@@ -5472,19 +5552,25 @@
         <v>0</v>
       </c>
       <c r="Q117">
-        <f t="shared" si="53"/>
+        <f t="shared" si="63"/>
         <v>5.4143472656250013</v>
       </c>
       <c r="R117">
-        <f t="shared" si="55"/>
+        <f t="shared" si="65"/>
         <v>0.11207698839843752</v>
       </c>
       <c r="S117">
-        <f t="shared" si="56"/>
+        <f t="shared" si="66"/>
         <v>629.87267479921888</v>
       </c>
+      <c r="AB117" s="3">
+        <v>1.3</v>
+      </c>
+      <c r="AC117" s="3">
+        <v>1.3</v>
+      </c>
       <c r="AF117">
-        <f t="shared" si="57"/>
+        <f t="shared" si="67"/>
         <v>629.87267479921888</v>
       </c>
     </row>

--- a/packages/calculators/src/modules/test/3.3-dairy-enteric.xlsx
+++ b/packages/calculators/src/modules/test/3.3-dairy-enteric.xlsx
@@ -3,11 +3,6 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eddiesholl/Code/aginnovationaustralia/emissions-calculators-internal/packages/calculators/src/modules/test/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{655AD9B2-1947-3C40-82A8-C6A8CA4971A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
